--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FF1AFC-C232-4D83-A870-644E98B4792C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E413205F-C3AC-4658-A43D-AE05A4D99EDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="82">
   <si>
     <t>HOJE</t>
   </si>
@@ -469,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -665,6 +665,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,7 +1008,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1279,11 +1285,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1386,18 +1392,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>0.05</v>
+        <v>4.9822064056939501E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1497,18 +1503,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>7.1770334928229665E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1571,7 +1577,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1606,7 +1612,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-177</v>
+        <v>-178</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1661,18 +1667,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.6393442622950821E-2</v>
+        <v>1.6304347826086956E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1693,7 +1699,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1724,18 +1730,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6393442622950821E-2</v>
+        <v>1.6304347826086956E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1756,18 +1762,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.6393442622950821E-2</v>
+        <v>1.6304347826086956E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2108,14 +2114,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2140,14 +2146,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2172,14 +2178,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2204,14 +2210,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2270,18 +2276,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2305,18 +2311,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2340,18 +2346,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2423,14 +2429,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2567,7 +2573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.7109375" style="47"/>
@@ -2581,25 +2587,25 @@
     <col min="10" max="16384" width="10.7109375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
-      <c r="G1" s="49">
+      <c r="G1" s="49" t="e">
         <f>SUM(I:I)</f>
-        <v>36</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H1" s="49" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2628,7 +2634,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>18</v>
       </c>
@@ -2643,14 +2649,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
         <f ca="1">E3-F3</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2659,7 +2665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2674,14 +2680,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
         <f ca="1">E4-F4</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2690,7 +2696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>18</v>
       </c>
@@ -2705,14 +2711,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
         <f ca="1">E5-F5</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2721,7 +2727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>18</v>
       </c>
@@ -2736,14 +2742,14 @@
       </c>
       <c r="E6" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F6" s="18">
         <v>46027</v>
       </c>
       <c r="G6" s="17">
         <f ca="1">E6-F6</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>54</v>
@@ -2752,7 +2758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -2767,14 +2773,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F7" s="18">
         <v>46036</v>
       </c>
       <c r="G7" s="17">
-        <f ca="1">F7-E7</f>
-        <v>-51</v>
+        <f ca="1">E7-F7</f>
+        <v>52</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>54</v>
@@ -2783,28 +2789,98 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+    <row r="8" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="18">
+        <f t="shared" ref="E8:E9" ca="1" si="0">TODAY()</f>
+        <v>46088</v>
+      </c>
+      <c r="F8" s="66">
+        <v>46082</v>
+      </c>
+      <c r="G8" s="17">
+        <f t="shared" ref="G8:G9" ca="1" si="1">E8-F8</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="65" t="e">
+        <f>J8/H8</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>46088</v>
+      </c>
+      <c r="F9" s="18">
+        <v>46088</v>
+      </c>
+      <c r="G9" s="17">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="17" t="e">
+        <f>J9/H9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B11" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C11" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D11" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E11" s="31">
         <v>45997</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H11" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2814,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="47" customWidth="1"/>
@@ -2836,7 +2912,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3029,35 +3105,66 @@
       <c r="F10" s="31"/>
       <c r="I10" s="32"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="47" t="s">
+    <row r="12" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="57">
         <v>46060</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="57">
         <v>46081</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="56">
         <f>F12-E12</f>
         <v>21</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="56">
         <v>12</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="58">
         <f>J12/H12</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="56">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="57">
+        <v>46067</v>
+      </c>
+      <c r="F13" s="57">
+        <v>46088</v>
+      </c>
+      <c r="G13" s="56">
+        <f>F13-E13</f>
+        <v>21</v>
+      </c>
+      <c r="H13" s="56">
+        <v>12</v>
+      </c>
+      <c r="I13" s="58">
+        <f>J13/H13</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J13" s="56">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3128,11 +3235,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3160,11 +3267,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E413205F-C3AC-4658-A43D-AE05A4D99EDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6585D74C-10B2-40DC-9588-FC8B5F7DA5D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="84">
   <si>
     <t>HOJE</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>Maria Rosa</t>
+  </si>
+  <si>
+    <t>nascidos</t>
+  </si>
+  <si>
+    <t>vivos</t>
   </si>
 </sst>
 </file>
@@ -669,8 +675,8 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2573,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.7109375" style="47"/>
@@ -2582,12 +2588,12 @@
     <col min="5" max="5" width="10.7109375" style="48"/>
     <col min="6" max="6" width="14.7109375" style="48" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" style="47"/>
-    <col min="8" max="8" width="12.42578125" style="47" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
     <col min="9" max="9" width="13.85546875" style="47" customWidth="1"/>
     <col min="10" max="16384" width="10.7109375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
@@ -2597,15 +2603,17 @@
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
-      <c r="G1" s="49" t="e">
-        <f>SUM(I:I)</f>
-        <v>#VALUE!</v>
+      <c r="G1" s="49">
+        <f>SUM(J7:J10)</f>
+        <v>14</v>
       </c>
       <c r="H1" s="49" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+    </row>
+    <row r="2" spans="1:11" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2631,10 +2639,13 @@
         <v>64</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J2" s="50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>18</v>
       </c>
@@ -2664,8 +2675,11 @@
       <c r="I3" s="17">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2695,8 +2709,11 @@
       <c r="I4" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>18</v>
       </c>
@@ -2726,47 +2743,53 @@
       <c r="I5" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="J5" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="66">
+        <f t="shared" ref="E6:E10" ca="1" si="0">TODAY()</f>
+        <v>46088</v>
+      </c>
+      <c r="F6" s="66">
+        <v>45910</v>
+      </c>
+      <c r="G6" s="65">
+        <f ca="1">E6-F6</f>
+        <v>178</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="65">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="18">
-        <f ca="1">TODAY()</f>
-        <v>46088</v>
-      </c>
-      <c r="F6" s="18">
-        <v>46027</v>
-      </c>
-      <c r="G6" s="17">
-        <f ca="1">E6-F6</f>
-        <v>61</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>29</v>
@@ -2776,63 +2799,65 @@
         <v>46088</v>
       </c>
       <c r="F7" s="18">
-        <v>46036</v>
+        <v>46027</v>
       </c>
       <c r="G7" s="17">
         <f ca="1">E7-F7</f>
+        <v>61</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="17">
+        <v>7</v>
+      </c>
+      <c r="J7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46088</v>
+      </c>
+      <c r="F8" s="18">
+        <v>46036</v>
+      </c>
+      <c r="G8" s="17">
+        <f ca="1">E8-F8</f>
         <v>52</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I8" s="17">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="65" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="18">
-        <f t="shared" ref="E8:E9" ca="1" si="0">TODAY()</f>
-        <v>46088</v>
-      </c>
-      <c r="F8" s="66">
-        <v>46082</v>
-      </c>
-      <c r="G8" s="17">
-        <f t="shared" ref="G8:G9" ca="1" si="1">E8-F8</f>
-        <v>6</v>
-      </c>
-      <c r="H8" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="65" t="e">
-        <f>J8/H8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="65">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>29</v>
@@ -2842,29 +2867,57 @@
         <v>46088</v>
       </c>
       <c r="F9" s="18">
+        <v>46082</v>
+      </c>
+      <c r="G9" s="17">
+        <f t="shared" ref="G9:G10" ca="1" si="1">E9-F9</f>
+        <v>6</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="17">
+        <v>10</v>
+      </c>
+      <c r="J9" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="18">
+        <f t="shared" ca="1" si="0"/>
         <v>46088</v>
       </c>
-      <c r="G9" s="17">
+      <c r="F10" s="18">
+        <v>46088</v>
+      </c>
+      <c r="G10" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="17" t="e">
-        <f>J9/H9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="17">
+      <c r="I10" s="17">
+        <v>7</v>
+      </c>
+      <c r="J10" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>35</v>
       </c>
@@ -2881,6 +2934,14 @@
         <v>45997</v>
       </c>
       <c r="H11" s="32"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6585D74C-10B2-40DC-9588-FC8B5F7DA5D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451FCF10-D848-4BE6-8D3E-634B6CDA3249}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -993,28 +993,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B71D903-D903-49BC-88F3-86B94027E03B}">
   <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="11.7109375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="15.453125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="16.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="2"/>
+    <col min="8" max="8" width="11.7265625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1030,7 +1030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>17</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>17</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>0.38095238095238093</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>18</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39" t="s">
         <v>17</v>
       </c>
@@ -1291,18 +1291,18 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>17</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>17</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>17</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>18</v>
       </c>
@@ -1398,21 +1398,21 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.9822064056939501E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+        <v>4.9645390070921988E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
         <v>18</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
         <v>18</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>0.61904761904761907</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>17</v>
       </c>
@@ -1509,24 +1509,24 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>7.1428571428571425E-2</v>
+        <v>7.1090047393364927E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="24" t="s">
         <v>17</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
         <v>18</v>
       </c>
@@ -1583,13 +1583,13 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-178</v>
+        <v>-179</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
         <v>18</v>
       </c>
@@ -1618,13 +1618,13 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-178</v>
+        <v>-179</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
         <v>18</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
         <v>22</v>
       </c>
@@ -1673,24 +1673,24 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.6304347826086956E-2</v>
+        <v>1.6216216216216217E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>22</v>
       </c>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>22</v>
       </c>
@@ -1736,24 +1736,24 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6304347826086956E-2</v>
+        <v>1.6216216216216217E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>22</v>
       </c>
@@ -1768,24 +1768,24 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.6304347826086956E-2</v>
+        <v>1.6216216216216217E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="28" t="s">
         <v>32</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
         <v>18</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
         <v>18</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
         <v>17</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
         <v>17</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="43" t="s">
         <v>17</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="19" t="s">
         <v>22</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
         <v>32</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
         <v>32</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
         <v>32</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
         <v>32</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
         <v>32</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
         <v>32</v>
       </c>
@@ -2120,14 +2120,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2140,7 +2140,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="17" t="s">
         <v>18</v>
       </c>
@@ -2152,14 +2152,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2172,7 +2172,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="17" t="s">
         <v>18</v>
       </c>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2204,7 +2204,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
         <v>18</v>
       </c>
@@ -2216,14 +2216,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2236,7 +2236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="15" t="s">
         <v>17</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="19" t="s">
         <v>22</v>
       </c>
@@ -2282,18 +2282,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2302,7 +2302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="19" t="s">
         <v>22</v>
       </c>
@@ -2317,18 +2317,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2337,7 +2337,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="19" t="s">
         <v>22</v>
       </c>
@@ -2352,18 +2352,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2372,7 +2372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="19" t="s">
         <v>22</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="15" t="s">
         <v>17</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17" t="s">
         <v>18</v>
       </c>
@@ -2435,14 +2435,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2455,11 +2455,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B52" s="36"/>
       <c r="H52" s="27"/>
     </row>
-    <row r="53" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="s">
         <v>35</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="s">
         <v>41</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30" t="s">
         <v>79</v>
       </c>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H55" s="32"/>
     </row>
-    <row r="56" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="s">
         <v>35</v>
       </c>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="H56" s="32"/>
     </row>
-    <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="s">
         <v>79</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="s">
         <v>79</v>
       </c>
@@ -2579,27 +2579,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" style="47"/>
-    <col min="3" max="3" width="17.42578125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="47"/>
-    <col min="5" max="5" width="10.7109375" style="48"/>
-    <col min="6" max="6" width="14.7109375" style="48" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="47"/>
-    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="47" customWidth="1"/>
-    <col min="10" max="16384" width="10.7109375" style="47"/>
+    <col min="1" max="2" width="10.7265625" style="47"/>
+    <col min="3" max="3" width="17.453125" style="47" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" style="47"/>
+    <col min="5" max="5" width="10.7265625" style="48"/>
+    <col min="6" max="6" width="14.7265625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" style="47"/>
+    <col min="8" max="8" width="15.1796875" style="47" customWidth="1"/>
+    <col min="9" max="9" width="13.81640625" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="10.7265625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2613,7 +2613,7 @@
       <c r="I1" s="67"/>
       <c r="J1" s="67"/>
     </row>
-    <row r="2" spans="1:11" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>18</v>
       </c>
@@ -2660,14 +2660,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
-        <f ca="1">E3-F3</f>
-        <v>141</v>
+        <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
+        <v>142</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2694,14 +2694,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
-        <f ca="1">E4-F4</f>
-        <v>135</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>136</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>18</v>
       </c>
@@ -2728,14 +2728,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
-        <f ca="1">E5-F5</f>
-        <v>132</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>133</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2747,7 +2747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="65" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="65" t="s">
         <v>18</v>
       </c>
@@ -2761,15 +2761,15 @@
         <v>30</v>
       </c>
       <c r="E6" s="66">
-        <f t="shared" ref="E6:E10" ca="1" si="0">TODAY()</f>
-        <v>46088</v>
+        <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
+        <v>46089</v>
       </c>
       <c r="F6" s="66">
         <v>45910</v>
       </c>
       <c r="G6" s="65">
-        <f ca="1">E6-F6</f>
-        <v>178</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>179</v>
       </c>
       <c r="H6" s="65" t="s">
         <v>54</v>
@@ -2781,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -2796,14 +2796,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F7" s="18">
         <v>46027</v>
       </c>
       <c r="G7" s="17">
-        <f ca="1">E7-F7</f>
-        <v>61</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>62</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -2815,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>18</v>
       </c>
@@ -2830,14 +2830,14 @@
       </c>
       <c r="E8" s="18">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F8" s="18">
         <v>46036</v>
       </c>
       <c r="G8" s="17">
-        <f ca="1">E8-F8</f>
-        <v>52</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -2849,7 +2849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2863,15 +2863,15 @@
         <v>29</v>
       </c>
       <c r="E9" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>46088</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46089</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
-        <f t="shared" ref="G9:G10" ca="1" si="1">E9-F9</f>
-        <v>6</v>
+        <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
+        <v>7</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2883,7 +2883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -2897,51 +2897,55 @@
         <v>29</v>
       </c>
       <c r="E10" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>46088</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46089</v>
       </c>
       <c r="F10" s="18">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="G10" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
       </c>
       <c r="I10" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B12" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C12" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D12" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E12" s="31">
         <v>45997</v>
       </c>
-      <c r="H11" s="32"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="23"/>
+      <c r="H12" s="32"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2952,28 +2956,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="47" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="47"/>
-    <col min="3" max="3" width="19.42578125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="47" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="47"/>
+    <col min="3" max="3" width="19.453125" style="47" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" style="47" customWidth="1"/>
     <col min="5" max="5" width="13" style="48" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="48" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" style="48" customWidth="1"/>
     <col min="7" max="7" width="13" style="47" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="47" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="47"/>
+    <col min="8" max="8" width="15.1796875" style="47" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2985,7 +2989,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="60" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
         <v>59</v>
       </c>
@@ -3017,7 +3021,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="56" t="s">
         <v>17</v>
       </c>
@@ -3051,7 +3055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="56" t="s">
         <v>17</v>
       </c>
@@ -3082,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="59" t="s">
         <v>17</v>
       </c>
@@ -3113,7 +3117,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>17</v>
       </c>
@@ -3147,7 +3151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>79</v>
       </c>
@@ -3166,7 +3170,7 @@
       <c r="F10" s="31"/>
       <c r="I10" s="32"/>
     </row>
-    <row r="12" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B12" s="56" t="s">
         <v>80</v>
       </c>
@@ -3197,7 +3201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>7</v>
       </c>
@@ -3237,21 +3241,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1ACAAB-4C7C-47DD-B348-5E0B06D77598}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="13.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="16.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="1"/>
+    <col min="8" max="8" width="9.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -3281,7 +3285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>22</v>
       </c>
@@ -3296,11 +3300,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3313,7 +3317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>22</v>
       </c>
@@ -3328,11 +3332,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>
@@ -3345,7 +3349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="s">
         <v>79</v>
       </c>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451FCF10-D848-4BE6-8D3E-634B6CDA3249}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892604-B4B3-497D-9538-420EAF582A26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="86">
   <si>
     <t>HOJE</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>vivos</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
   </si>
 </sst>
 </file>
@@ -475,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -651,22 +657,10 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1014,7 +1008,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1291,11 +1285,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1398,18 +1392,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.9645390070921988E-2</v>
+        <v>4.6666666666666669E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1509,18 +1503,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>7.1090047393364927E-2</v>
+        <v>6.5502183406113537E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1583,7 +1577,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-179</v>
+        <v>-197</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1618,7 +1612,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-179</v>
+        <v>-197</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1673,18 +1667,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.6216216216216217E-2</v>
+        <v>1.4778325123152709E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1705,7 +1699,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1736,18 +1730,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6216216216216217E-2</v>
+        <v>1.4778325123152709E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1768,18 +1762,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.6216216216216217E-2</v>
+        <v>1.4778325123152709E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2120,14 +2114,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2152,14 +2146,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2184,14 +2178,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2216,14 +2210,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2282,18 +2276,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2317,18 +2311,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2352,18 +2346,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2435,14 +2429,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2599,7 +2593,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2610,8 +2604,8 @@
       <c r="H1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
@@ -2660,14 +2654,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2694,14 +2688,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2728,14 +2722,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2747,37 +2741,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="65" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="65" t="s">
+    <row r="6" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="62">
         <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46089</v>
-      </c>
-      <c r="F6" s="66">
+        <v>46107</v>
+      </c>
+      <c r="F6" s="62">
         <v>45910</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="61">
         <f t="shared" ca="1" si="0"/>
-        <v>179</v>
-      </c>
-      <c r="H6" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="61">
         <v>6</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="61">
         <v>1</v>
       </c>
     </row>
@@ -2796,14 +2790,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F7" s="18">
         <v>46027</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -2830,14 +2824,14 @@
       </c>
       <c r="E8" s="18">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F8" s="18">
         <v>46036</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -2864,14 +2858,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2898,14 +2892,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2955,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -2977,7 +2971,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2989,35 +2983,35 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="60" t="s">
+    <row r="2" spans="1:10" s="59" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="59" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3086,149 +3080,211 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="59" t="s">
+    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E5" s="16">
         <v>46005</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F5" s="16">
         <v>46026</v>
       </c>
-      <c r="G7" s="62">
-        <f>F7-E7</f>
+      <c r="G5" s="15">
+        <f>F5-E5</f>
         <v>21</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H5" s="15">
         <v>10</v>
       </c>
-      <c r="I7" s="64" t="e">
-        <f>#REF!/H7</f>
+      <c r="I5" s="33" t="e">
+        <f>#REF!/H5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
+    <row r="6" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E6" s="16">
         <v>46015</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F6" s="16">
         <v>46036</v>
       </c>
-      <c r="G8" s="15">
-        <f>F8-E8</f>
+      <c r="G6" s="15">
+        <f>F6-E6</f>
         <v>21</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H6" s="15">
         <v>10</v>
       </c>
-      <c r="I8" s="33">
-        <f>J8/H8</f>
+      <c r="I6" s="33">
+        <f>J6/H6</f>
         <v>0.9</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J6" s="15">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+    <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="16">
+        <v>46198</v>
+      </c>
+      <c r="F9" s="16">
+        <v>46219</v>
+      </c>
+      <c r="G9" s="15">
+        <f>F9-E9</f>
+        <v>21</v>
+      </c>
+      <c r="H9" s="15">
+        <v>13</v>
+      </c>
+      <c r="I9" s="33">
+        <f>J9/H9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="16">
+        <v>46198</v>
+      </c>
+      <c r="F10" s="16">
+        <v>46219</v>
+      </c>
+      <c r="G10" s="15">
+        <f>F10-E10</f>
+        <v>21</v>
+      </c>
+      <c r="H10" s="15">
+        <v>13</v>
+      </c>
+      <c r="I10" s="33">
+        <f>J10/H10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B12" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C12" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D12" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E12" s="31">
         <v>45996</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="I10" s="32"/>
-    </row>
-    <row r="12" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="56" t="s">
+      <c r="F12" s="31"/>
+      <c r="I12" s="32"/>
+    </row>
+    <row r="14" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C14" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D14" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E14" s="57">
         <v>46060</v>
       </c>
-      <c r="F12" s="57">
+      <c r="F14" s="57">
         <v>46081</v>
       </c>
-      <c r="G12" s="56">
-        <f>F12-E12</f>
+      <c r="G14" s="56">
+        <f>F14-E14</f>
         <v>21</v>
       </c>
-      <c r="H12" s="56">
+      <c r="H14" s="56">
         <v>12</v>
       </c>
-      <c r="I12" s="58">
-        <f>J12/H12</f>
+      <c r="I14" s="58">
+        <f>J14/H14</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J12" s="56">
+      <c r="J14" s="56">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="56" t="s">
+    <row r="15" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C15" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D15" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E15" s="57">
         <v>46067</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F15" s="57">
         <v>46088</v>
       </c>
-      <c r="G13" s="56">
-        <f>F13-E13</f>
+      <c r="G15" s="56">
+        <f>F15-E15</f>
         <v>21</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H15" s="56">
         <v>12</v>
       </c>
-      <c r="I13" s="58">
-        <f>J13/H13</f>
+      <c r="I15" s="58">
+        <f>J15/H15</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J13" s="56">
+      <c r="J15" s="56">
         <v>5</v>
       </c>
     </row>
@@ -3300,11 +3356,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3332,11 +3388,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46107</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892604-B4B3-497D-9538-420EAF582A26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435EA6BC-3541-45F7-A0AD-DF7FEAF76FFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -298,7 +298,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +386,21 @@
       <b/>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="0.59999389629810485"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="0.59999389629810485"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -481,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -671,6 +686,30 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3015,135 +3054,139 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="56" t="s">
+    <row r="3" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="65">
         <v>45955</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="65">
         <v>45977</v>
       </c>
-      <c r="G3" s="56">
+      <c r="G3" s="64">
         <f>F3-E3</f>
         <v>22</v>
       </c>
-      <c r="H3" s="56">
+      <c r="H3" s="64">
         <v>10</v>
       </c>
-      <c r="I3" s="58">
+      <c r="I3" s="66">
         <f>J3/H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="64">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56" t="s">
+    <row r="4" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="65">
         <v>45982</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="65">
         <v>46003</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="64">
         <f>F4-E4</f>
         <v>21</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="64">
         <v>10</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="66">
         <f>J4/H4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="56" t="s">
+    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="68">
         <v>46005</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="68">
         <v>46026</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="67">
         <f>F5-E5</f>
         <v>21</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="67">
         <v>10</v>
       </c>
-      <c r="I5" s="33" t="e">
+      <c r="I5" s="69" t="e">
         <f>#REF!/H5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="68">
         <v>46015</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="68">
         <v>46036</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="67">
         <f>F6-E6</f>
         <v>21</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="67">
         <v>10</v>
       </c>
-      <c r="I6" s="33">
+      <c r="I6" s="69">
         <f>J6/H6</f>
         <v>0.9</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="67">
         <v>9</v>
       </c>
+    </row>
+    <row r="7" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
     </row>
     <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
@@ -3159,10 +3202,10 @@
         <v>29</v>
       </c>
       <c r="E9" s="16">
-        <v>46198</v>
+        <v>46106</v>
       </c>
       <c r="F9" s="16">
-        <v>46219</v>
+        <v>46127</v>
       </c>
       <c r="G9" s="15">
         <f>F9-E9</f>
@@ -3190,10 +3233,10 @@
         <v>34</v>
       </c>
       <c r="E10" s="16">
-        <v>46198</v>
+        <v>46106</v>
       </c>
       <c r="F10" s="16">
-        <v>46219</v>
+        <v>46127</v>
       </c>
       <c r="G10" s="15">
         <f>F10-E10</f>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435EA6BC-3541-45F7-A0AD-DF7FEAF76FFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00937941-ACBD-4EFE-8930-D72B52A3365C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -298,7 +298,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,22 +370,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -496,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -663,15 +647,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -687,28 +662,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1047,7 +1022,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1324,11 +1299,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1431,18 +1406,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.6666666666666669E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1542,18 +1517,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>6.5502183406113537E-2</v>
+        <v>6.3291139240506333E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1616,7 +1591,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-197</v>
+        <v>-205</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1651,7 +1626,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-197</v>
+        <v>-205</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1706,18 +1681,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.4778325123152709E-2</v>
+        <v>1.4218009478672985E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1738,7 +1713,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1769,18 +1744,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.4778325123152709E-2</v>
+        <v>1.4218009478672985E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1801,18 +1776,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.4778325123152709E-2</v>
+        <v>1.4218009478672985E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2153,14 +2128,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2185,14 +2160,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2217,14 +2192,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2249,14 +2224,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2315,18 +2290,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2350,18 +2325,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2385,18 +2360,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2468,14 +2443,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2632,7 +2607,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2643,8 +2618,8 @@
       <c r="H1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
     </row>
     <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
@@ -2693,14 +2668,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2727,14 +2702,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2761,14 +2736,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2780,37 +2755,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="61" t="s">
+    <row r="6" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="59">
         <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46107</v>
-      </c>
-      <c r="F6" s="62">
+        <v>46115</v>
+      </c>
+      <c r="F6" s="59">
         <v>45910</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="58">
         <f t="shared" ca="1" si="0"/>
-        <v>197</v>
-      </c>
-      <c r="H6" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="H6" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="58">
         <v>6</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="58">
         <v>1</v>
       </c>
     </row>
@@ -2829,14 +2804,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F7" s="18">
         <v>46027</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -2863,14 +2838,14 @@
       </c>
       <c r="E8" s="18">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F8" s="18">
         <v>46036</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -2897,14 +2872,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2931,14 +2906,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -3010,7 +2985,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3022,171 +2997,171 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="59" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="59" t="s">
+    <row r="2" spans="1:10" s="56" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="J2" s="56" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="62">
         <v>45955</v>
       </c>
-      <c r="F3" s="65">
+      <c r="F3" s="62">
         <v>45977</v>
       </c>
-      <c r="G3" s="64">
+      <c r="G3" s="61">
         <f>F3-E3</f>
         <v>22</v>
       </c>
-      <c r="H3" s="64">
+      <c r="H3" s="61">
         <v>10</v>
       </c>
-      <c r="I3" s="66">
+      <c r="I3" s="63">
         <f>J3/H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="61">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="64" t="s">
+    <row r="4" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="62">
         <v>45982</v>
       </c>
-      <c r="F4" s="65">
+      <c r="F4" s="62">
         <v>46003</v>
       </c>
-      <c r="G4" s="64">
+      <c r="G4" s="61">
         <f>F4-E4</f>
         <v>21</v>
       </c>
-      <c r="H4" s="64">
+      <c r="H4" s="61">
         <v>10</v>
       </c>
-      <c r="I4" s="66">
+      <c r="I4" s="63">
         <f>J4/H4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="64" t="s">
+    <row r="5" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="65">
         <v>46005</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="65">
         <v>46026</v>
       </c>
-      <c r="G5" s="67">
+      <c r="G5" s="64">
         <f>F5-E5</f>
         <v>21</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="64">
         <v>10</v>
       </c>
-      <c r="I5" s="69" t="e">
+      <c r="I5" s="66" t="e">
         <f>#REF!/H5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="67" t="s">
+    <row r="6" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="65">
         <v>46015</v>
       </c>
-      <c r="F6" s="68">
+      <c r="F6" s="65">
         <v>46036</v>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="64">
         <f>F6-E6</f>
         <v>21</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="64">
         <v>10</v>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="66">
         <f>J6/H6</f>
         <v>0.9</v>
       </c>
-      <c r="J6" s="67">
+      <c r="J6" s="64">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
     </row>
     <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
@@ -3269,65 +3244,66 @@
       <c r="F12" s="31"/>
       <c r="I12" s="32"/>
     </row>
-    <row r="14" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="56" t="s">
+    <row r="14" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="61"/>
+      <c r="B14" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="65">
         <v>46060</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="65">
         <v>46081</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="64">
         <f>F14-E14</f>
         <v>21</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="64">
         <v>12</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14" s="66">
         <f>J14/H14</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="64">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="56" t="s">
+    <row r="15" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="65">
         <v>46067</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="65">
         <v>46088</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="64">
         <f>F15-E15</f>
         <v>21</v>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="64">
         <v>12</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="66">
         <f>J15/H15</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="64">
         <v>5</v>
       </c>
     </row>
@@ -3399,11 +3375,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3431,11 +3407,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00937941-ACBD-4EFE-8930-D72B52A3365C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFE9A05-26D0-4D91-BE25-313FC888A810}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="88">
   <si>
     <t>HOJE</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>Fernanda</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Filomena</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1028,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1299,11 +1305,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1406,18 +1412,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5454545454545456E-2</v>
+        <v>4.4444444444444446E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1517,18 +1523,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>6.3291139240506333E-2</v>
+        <v>6.1475409836065573E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1591,7 +1597,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-205</v>
+        <v>-212</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1626,7 +1632,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-205</v>
+        <v>-212</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1681,18 +1687,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.4218009478672985E-2</v>
+        <v>1.3761467889908258E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1713,7 +1719,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1744,18 +1750,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.4218009478672985E-2</v>
+        <v>1.3761467889908258E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1776,18 +1782,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.4218009478672985E-2</v>
+        <v>1.3761467889908258E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2128,14 +2134,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2160,14 +2166,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2192,14 +2198,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2224,14 +2230,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2290,18 +2296,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2325,18 +2331,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2360,18 +2366,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2443,14 +2449,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2607,7 +2613,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2668,14 +2674,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2702,14 +2708,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2736,14 +2742,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2770,14 +2776,14 @@
       </c>
       <c r="E6" s="59">
         <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F6" s="59">
         <v>45910</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ca="1" si="0"/>
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H6" s="58" t="s">
         <v>54</v>
@@ -2804,14 +2810,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F7" s="18">
         <v>46027</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -2838,14 +2844,14 @@
       </c>
       <c r="E8" s="18">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F8" s="18">
         <v>46036</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -2872,14 +2878,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2906,14 +2912,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2963,7 +2969,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -2985,7 +2991,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3225,72 +3231,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
+    <row r="11" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="16">
+        <v>46122</v>
+      </c>
+      <c r="F11" s="16">
+        <v>46143</v>
+      </c>
+      <c r="G11" s="15">
+        <f>F11-E11</f>
+        <v>21</v>
+      </c>
+      <c r="H11" s="15">
+        <v>13</v>
+      </c>
+      <c r="I11" s="33">
+        <f>J11/H11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B13" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C13" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D13" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E13" s="31">
         <v>45996</v>
       </c>
-      <c r="F12" s="31"/>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="14" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="61"/>
-      <c r="B14" s="64" t="s">
+      <c r="F13" s="31"/>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="15" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="61"/>
+      <c r="B15" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C15" s="64" t="s">
         <v>81</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="65">
-        <v>46060</v>
-      </c>
-      <c r="F14" s="65">
-        <v>46081</v>
-      </c>
-      <c r="G14" s="64">
-        <f>F14-E14</f>
-        <v>21</v>
-      </c>
-      <c r="H14" s="64">
-        <v>12</v>
-      </c>
-      <c r="I14" s="66">
-        <f>J14/H14</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J14" s="64">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>8</v>
       </c>
       <c r="D15" s="64" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="65">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F15" s="65">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G15" s="64">
         <f>F15-E15</f>
@@ -3301,9 +3307,40 @@
       </c>
       <c r="I15" s="66">
         <f>J15/H15</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J15" s="64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="65">
+        <v>46067</v>
+      </c>
+      <c r="F16" s="65">
+        <v>46088</v>
+      </c>
+      <c r="G16" s="64">
+        <f>F16-E16</f>
+        <v>21</v>
+      </c>
+      <c r="H16" s="64">
+        <v>12</v>
+      </c>
+      <c r="I16" s="66">
+        <f>J16/H16</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J16" s="64">
         <v>5</v>
       </c>
     </row>
@@ -3375,11 +3412,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3407,11 +3444,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFE9A05-26D0-4D91-BE25-313FC888A810}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AB809E-86EB-4039-A250-2B4B264946E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="88">
   <si>
     <t>HOJE</t>
   </si>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1305,11 +1305,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1412,18 +1412,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.4444444444444446E-2</v>
+        <v>4.40251572327044E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1523,18 +1523,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>6.1475409836065573E-2</v>
+        <v>6.0728744939271252E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1687,18 +1687,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.3761467889908258E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1750,18 +1750,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.3761467889908258E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1782,18 +1782,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.3761467889908258E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2134,14 +2134,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2166,14 +2166,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2230,14 +2230,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2296,18 +2296,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2331,18 +2331,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2366,18 +2366,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2449,14 +2449,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2674,14 +2674,14 @@
       </c>
       <c r="E3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F3" s="18">
         <v>45947</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>54</v>
@@ -2708,14 +2708,14 @@
       </c>
       <c r="E4" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F4" s="18">
         <v>45953</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>54</v>
@@ -2742,14 +2742,14 @@
       </c>
       <c r="E5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F5" s="18">
         <v>45956</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>54</v>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="E6" s="59">
         <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F6" s="59">
         <v>45910</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ca="1" si="0"/>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H6" s="58" t="s">
         <v>54</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="E7" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F7" s="18">
         <v>46027</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="E8" s="18">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F8" s="18">
         <v>46036</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2969,7 +2969,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3185,7 +3185,7 @@
       <c r="E9" s="16">
         <v>46106</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="18">
         <v>46127</v>
       </c>
       <c r="G9" s="15">
@@ -3216,7 +3216,7 @@
       <c r="E10" s="16">
         <v>46106</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="18">
         <v>46127</v>
       </c>
       <c r="G10" s="15">
@@ -3262,72 +3262,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="30" t="s">
+    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="16">
+        <v>46124</v>
+      </c>
+      <c r="F12" s="16">
+        <v>46145</v>
+      </c>
+      <c r="G12" s="15">
+        <f>F12-E12</f>
+        <v>21</v>
+      </c>
+      <c r="H12" s="15">
+        <v>13</v>
+      </c>
+      <c r="I12" s="33">
+        <f>J12/H12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B14" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C14" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D14" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E14" s="31">
         <v>45996</v>
       </c>
-      <c r="F13" s="31"/>
-      <c r="I13" s="32"/>
-    </row>
-    <row r="15" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="61"/>
-      <c r="B15" s="64" t="s">
+      <c r="F14" s="31"/>
+      <c r="I14" s="32"/>
+    </row>
+    <row r="16" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="61"/>
+      <c r="B16" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C16" s="64" t="s">
         <v>81</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="65">
-        <v>46060</v>
-      </c>
-      <c r="F15" s="65">
-        <v>46081</v>
-      </c>
-      <c r="G15" s="64">
-        <f>F15-E15</f>
-        <v>21</v>
-      </c>
-      <c r="H15" s="64">
-        <v>12</v>
-      </c>
-      <c r="I15" s="66">
-        <f>J15/H15</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J15" s="64">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>8</v>
       </c>
       <c r="D16" s="64" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="65">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F16" s="65">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G16" s="64">
         <f>F16-E16</f>
@@ -3338,9 +3338,40 @@
       </c>
       <c r="I16" s="66">
         <f>J16/H16</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J16" s="64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="65">
+        <v>46067</v>
+      </c>
+      <c r="F17" s="65">
+        <v>46088</v>
+      </c>
+      <c r="G17" s="64">
+        <f>F17-E17</f>
+        <v>21</v>
+      </c>
+      <c r="H17" s="64">
+        <v>12</v>
+      </c>
+      <c r="I17" s="66">
+        <f>J17/H17</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J17" s="64">
         <v>5</v>
       </c>
     </row>
@@ -3412,11 +3443,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3444,11 +3475,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AB809E-86EB-4039-A250-2B4B264946E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D26F5F-8041-40A4-A4E7-BDCA13075D63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="88">
   <si>
     <t>HOJE</t>
   </si>
@@ -304,7 +304,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,6 +391,21 @@
     <font>
       <sz val="11"/>
       <color theme="4" tint="0.59999389629810485"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -486,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -659,12 +674,6 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -691,6 +700,27 @@
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,7 +1058,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1305,11 +1335,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1412,18 +1442,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.40251572327044E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1523,18 +1553,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>6.0728744939271252E-2</v>
+        <v>5.9760956175298807E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1597,7 +1627,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-215</v>
+        <v>-219</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1632,7 +1662,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-215</v>
+        <v>-219</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1687,18 +1717,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1719,7 +1749,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1750,18 +1780,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1782,18 +1812,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2134,14 +2164,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2166,14 +2196,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2198,14 +2228,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2230,14 +2260,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2296,18 +2326,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2331,18 +2361,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2366,18 +2396,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2449,14 +2479,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2593,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.7265625" style="47"/>
@@ -2607,13 +2637,13 @@
     <col min="10" max="16384" width="10.7265625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2624,10 +2654,10 @@
       <c r="H1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-    </row>
-    <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+    </row>
+    <row r="2" spans="1:10" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2659,211 +2689,211 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F3" s="18">
+        <v>46129</v>
+      </c>
+      <c r="F3" s="68">
         <v>45947</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>178</v>
-      </c>
-      <c r="H3" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="67">
         <v>4</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F4" s="18">
+        <v>46129</v>
+      </c>
+      <c r="F4" s="68">
         <v>45953</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>172</v>
-      </c>
-      <c r="H4" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="67">
         <v>8</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F5" s="18">
+        <v>46129</v>
+      </c>
+      <c r="F5" s="68">
         <v>45956</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>169</v>
-      </c>
-      <c r="H5" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="67">
         <v>8</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="67">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="58" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="58" t="s">
+    <row r="6" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="71">
         <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F6" s="59">
+        <v>46129</v>
+      </c>
+      <c r="F6" s="71">
         <v>45910</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>215</v>
-      </c>
-      <c r="H6" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="70">
         <v>6</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="70">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F7" s="18">
+        <v>46129</v>
+      </c>
+      <c r="F7" s="68">
         <v>46027</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="H7" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="67">
         <v>7</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="67">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="68">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="F8" s="18">
+        <v>46129</v>
+      </c>
+      <c r="F8" s="68">
         <v>46036</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
-      </c>
-      <c r="H8" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="67">
         <v>9</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="67">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2878,14 +2908,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2897,7 +2927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -2912,14 +2942,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2931,35 +2961,83 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-    </row>
-    <row r="12" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
+    <row r="11" spans="1:10" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="73">
+        <v>46106</v>
+      </c>
+      <c r="F11" s="73">
+        <v>46129</v>
+      </c>
+      <c r="G11" s="72">
+        <f>F11-E11</f>
+        <v>23</v>
+      </c>
+      <c r="H11" s="72">
+        <v>13</v>
+      </c>
+      <c r="I11" s="72">
+        <v>8</v>
+      </c>
+      <c r="J11" s="72">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="16"/>
+      <c r="F12" s="18"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="16"/>
+      <c r="F13" s="18"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="16"/>
+      <c r="F14" s="18"/>
+      <c r="I14" s="33"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B16" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C16" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D16" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E16" s="31">
         <v>45997</v>
       </c>
-      <c r="H12" s="32"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F15" s="18"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="23"/>
+      <c r="H16" s="32"/>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2969,7 +3047,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -2991,7 +3069,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3035,169 +3113,172 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="61" t="s">
+    <row r="3" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="60">
         <v>45955</v>
       </c>
-      <c r="F3" s="62">
+      <c r="F3" s="60">
         <v>45977</v>
       </c>
-      <c r="G3" s="61">
+      <c r="G3" s="59">
         <f>F3-E3</f>
         <v>22</v>
       </c>
-      <c r="H3" s="61">
+      <c r="H3" s="59">
         <v>10</v>
       </c>
-      <c r="I3" s="63">
+      <c r="I3" s="61">
         <f>J3/H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="61">
+      <c r="J3" s="59">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="61" t="s">
+    <row r="4" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="62">
+      <c r="E4" s="60">
         <v>45982</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="60">
         <v>46003</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="59">
         <f>F4-E4</f>
         <v>21</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="59">
         <v>10</v>
       </c>
-      <c r="I4" s="63">
+      <c r="I4" s="61">
         <f>J4/H4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="61" t="s">
+    <row r="5" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="63">
         <v>46005</v>
       </c>
-      <c r="F5" s="65">
+      <c r="F5" s="63">
         <v>46026</v>
       </c>
-      <c r="G5" s="64">
+      <c r="G5" s="62">
         <f>F5-E5</f>
         <v>21</v>
       </c>
-      <c r="H5" s="64">
+      <c r="H5" s="62">
         <v>10</v>
       </c>
-      <c r="I5" s="66" t="e">
+      <c r="I5" s="64" t="e">
         <f>#REF!/H5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64" t="s">
+    <row r="6" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="63">
         <v>46015</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="63">
         <v>46036</v>
       </c>
-      <c r="G6" s="64">
+      <c r="G6" s="62">
         <f>F6-E6</f>
         <v>21</v>
       </c>
-      <c r="H6" s="64">
+      <c r="H6" s="62">
         <v>10</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="64">
         <f>J6/H6</f>
         <v>0.9</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="62">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-    </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
+    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+    </row>
+    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="68">
         <v>46106</v>
       </c>
-      <c r="F9" s="18">
-        <v>46127</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="F9" s="68">
+        <v>46129</v>
+      </c>
+      <c r="G9" s="67">
         <f>F9-E9</f>
-        <v>21</v>
-      </c>
-      <c r="H9" s="15">
+        <v>23</v>
+      </c>
+      <c r="H9" s="67">
         <v>13</v>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="69">
         <f>J9/H9</f>
-        <v>0</v>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="J9" s="67">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
@@ -3293,85 +3374,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
+    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="16" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B16" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C16" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D16" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E16" s="31">
         <v>45996</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="I14" s="32"/>
-    </row>
-    <row r="16" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="61"/>
-      <c r="B16" s="64" t="s">
+      <c r="F16" s="31"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="18" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="59"/>
+      <c r="B18" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C18" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D18" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E18" s="63">
         <v>46060</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F18" s="63">
         <v>46081</v>
       </c>
-      <c r="G16" s="64">
-        <f>F16-E16</f>
+      <c r="G18" s="62">
+        <f>F18-E18</f>
         <v>21</v>
       </c>
-      <c r="H16" s="64">
+      <c r="H18" s="62">
         <v>12</v>
       </c>
-      <c r="I16" s="66">
-        <f>J16/H16</f>
+      <c r="I18" s="64">
+        <f>J18/H18</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J18" s="62">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:10" s="64" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="64" t="s">
+    <row r="19" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C19" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="64" t="s">
+      <c r="D19" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E19" s="63">
         <v>46067</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F19" s="63">
         <v>46088</v>
       </c>
-      <c r="G17" s="64">
-        <f>F17-E17</f>
+      <c r="G19" s="62">
+        <f>F19-E19</f>
         <v>21</v>
       </c>
-      <c r="H17" s="64">
+      <c r="H19" s="62">
         <v>12</v>
       </c>
-      <c r="I17" s="66">
-        <f>J17/H17</f>
+      <c r="I19" s="64">
+        <f>J19/H19</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J17" s="64">
+      <c r="J19" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3443,11 +3529,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3475,11 +3561,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D26F5F-8041-40A4-A4E7-BDCA13075D63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E682C0FA-C197-48AA-A00F-EAE73F03CC5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="88">
   <si>
     <t>HOJE</t>
   </si>
@@ -501,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -720,6 +720,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2859,37 +2865,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="67" t="s">
+    <row r="8" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="75">
         <f ca="1">TODAY()</f>
         <v>46129</v>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="75">
         <v>46036</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>93</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="67">
+      <c r="I8" s="74">
         <v>9</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="74">
         <v>3</v>
       </c>
     </row>
@@ -2994,10 +3000,32 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
-      <c r="I12" s="33"/>
+    <row r="12" spans="1:10" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="73">
+        <v>46106</v>
+      </c>
+      <c r="F12" s="73">
+        <v>46129</v>
+      </c>
+      <c r="G12" s="72">
+        <f>F12-E12</f>
+        <v>23</v>
+      </c>
+      <c r="H12" s="72">
+        <v>13</v>
+      </c>
+      <c r="I12" s="72">
+        <v>3</v>
+      </c>
+      <c r="J12" s="72">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="E13" s="16"/>
@@ -3281,64 +3309,67 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="68">
         <v>46106</v>
       </c>
-      <c r="F10" s="18">
-        <v>46127</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="F10" s="68">
+        <v>46129</v>
+      </c>
+      <c r="G10" s="67">
         <f>F10-E10</f>
-        <v>21</v>
-      </c>
-      <c r="H10" s="15">
+        <v>23</v>
+      </c>
+      <c r="H10" s="67">
         <v>13</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="69">
         <f>J10/H10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="J10" s="67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="18">
         <v>46122</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="18">
         <v>46143</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="17">
         <f>F11-E11</f>
         <v>21</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="17">
         <v>13</v>
       </c>
-      <c r="I11" s="33">
+      <c r="I11" s="22">
         <f>J11/H11</f>
         <v>0</v>
       </c>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E682C0FA-C197-48AA-A00F-EAE73F03CC5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CB6D2C-3BE5-4340-8B48-12489AF69BA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.3478260869565216E-2</v>
+        <v>4.2944785276073622E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1559,18 +1559,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.9760956175298807E-2</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-219</v>
+        <v>-223</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-219</v>
+        <v>-223</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1723,18 +1723,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.3333333333333334E-2</v>
+        <v>1.3100436681222707E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1786,18 +1786,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.3333333333333334E-2</v>
+        <v>1.3100436681222707E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1818,18 +1818,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.3333333333333334E-2</v>
+        <v>1.3100436681222707E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2202,14 +2202,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2332,18 +2332,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2367,18 +2367,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2402,18 +2402,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2485,14 +2485,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2778,14 +2778,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2811,15 +2811,15 @@
         <v>30</v>
       </c>
       <c r="E6" s="71">
-        <f t="shared" ref="E6:E10" ca="1" si="1">TODAY()</f>
-        <v>46129</v>
+        <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
+        <v>46133</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2846,14 +2846,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2880,14 +2880,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2914,14 +2914,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
-        <f t="shared" ref="G9:G10" ca="1" si="2">E9-F9</f>
-        <v>47</v>
+        <f ca="1">E9-F9</f>
+        <v>51</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2948,14 +2948,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <f t="shared" ref="G9:G12" ca="1" si="2">E10-F10</f>
+        <v>44</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2980,15 +2980,16 @@
       <c r="D11" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="73">
-        <v>46106</v>
+      <c r="E11" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>46133</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
-      <c r="G11" s="72">
-        <f>F11-E11</f>
-        <v>23</v>
+      <c r="G11" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3007,15 +3008,16 @@
       <c r="D12" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="73">
-        <v>46106</v>
+      <c r="E12" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>46133</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
-      <c r="G12" s="72">
-        <f>F12-E12</f>
-        <v>23</v>
+      <c r="G12" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3097,7 +3099,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3560,11 +3562,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3592,11 +3594,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CB6D2C-3BE5-4340-8B48-12489AF69BA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CADC93A-BBAD-47BD-AFA2-63767F2B06F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.2944785276073622E-2</v>
+        <v>4.1543026706231452E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1559,18 +1559,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.8823529411764705E-2</v>
+        <v>5.6390977443609019E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-223</v>
+        <v>-234</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-223</v>
+        <v>-234</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1723,18 +1723,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.3100436681222707E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1786,18 +1786,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.3100436681222707E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1818,18 +1818,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.3100436681222707E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2202,14 +2202,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2332,18 +2332,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2367,18 +2367,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2402,18 +2402,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2485,14 +2485,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2778,14 +2778,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2812,14 +2812,14 @@
       </c>
       <c r="E6" s="71">
         <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2846,14 +2846,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2880,14 +2880,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2914,14 +2914,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f ca="1">E9-F9</f>
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2948,14 +2948,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
-        <f t="shared" ref="G9:G12" ca="1" si="2">E10-F10</f>
-        <v>44</v>
+        <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
+        <v>55</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2982,14 +2982,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3010,14 +3010,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3362,11 +3362,11 @@
         <v>46122</v>
       </c>
       <c r="F11" s="18">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="G11" s="17">
         <f>F11-E11</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="17">
         <v>13</v>
@@ -3562,11 +3562,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3594,11 +3594,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46144</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CADC93A-BBAD-47BD-AFA2-63767F2B06F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A321529-A908-41D8-82AD-A0A1A199A7F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.1543026706231452E-2</v>
+        <v>4.1297935103244837E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1559,18 +1559,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.6390977443609019E-2</v>
+        <v>5.5970149253731345E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-234</v>
+        <v>-236</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-234</v>
+        <v>-236</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1723,18 +1723,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.2500000000000001E-2</v>
+        <v>1.2396694214876033E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1786,18 +1786,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.2500000000000001E-2</v>
+        <v>1.2396694214876033E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1818,18 +1818,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.2500000000000001E-2</v>
+        <v>1.2396694214876033E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2202,14 +2202,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2332,18 +2332,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2367,18 +2367,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2402,18 +2402,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2485,14 +2485,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2710,14 +2710,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2744,14 +2744,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2778,14 +2778,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2812,14 +2812,14 @@
       </c>
       <c r="E6" s="71">
         <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2846,14 +2846,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2880,14 +2880,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2914,14 +2914,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f ca="1">E9-F9</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2948,14 +2948,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2982,14 +2982,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3010,14 +3010,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3373,7 +3373,10 @@
       </c>
       <c r="I11" s="22">
         <f>J11/H11</f>
-        <v>0</v>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="J11" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
@@ -3404,7 +3407,10 @@
       </c>
       <c r="I12" s="33">
         <f>J12/H12</f>
-        <v>0</v>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="J12" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
@@ -3562,11 +3568,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3594,11 +3600,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A321529-A908-41D8-82AD-A0A1A199A7F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE80E6F-E6BB-4249-82C0-2759B19EDC48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="90">
   <si>
     <t>HOJE</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>Filomena</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Flávia</t>
   </si>
 </sst>
 </file>
@@ -501,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -727,6 +733,12 @@
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,7 +1076,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1341,11 +1353,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1448,18 +1460,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>4.1297935103244837E-2</v>
+        <v>3.9772727272727272E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1559,18 +1571,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.5970149253731345E-2</v>
+        <v>5.3380782918149468E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1633,7 +1645,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-236</v>
+        <v>-249</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1668,7 +1680,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-236</v>
+        <v>-249</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1723,18 +1735,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.2396694214876033E-2</v>
+        <v>1.1764705882352941E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1755,7 +1767,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1786,18 +1798,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.2396694214876033E-2</v>
+        <v>1.1764705882352941E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1818,18 +1830,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.2396694214876033E-2</v>
+        <v>1.1764705882352941E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2170,14 +2182,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2202,14 +2214,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2234,14 +2246,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2266,14 +2278,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2332,18 +2344,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>674</v>
+        <v>700</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2367,18 +2379,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2402,18 +2414,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2485,14 +2497,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2649,7 +2661,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2710,14 +2722,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2744,14 +2756,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2778,14 +2790,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2812,14 +2824,14 @@
       </c>
       <c r="E6" s="71">
         <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2846,14 +2858,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2880,14 +2892,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2914,14 +2926,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f ca="1">E9-F9</f>
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2948,14 +2960,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2982,14 +2994,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3010,14 +3022,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3099,7 +3111,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3345,37 +3357,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="68">
         <v>46122</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="68">
         <v>46144</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="67">
         <f>F11-E11</f>
         <v>22</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="67">
         <v>13</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="69">
         <f>J11/H11</f>
         <v>0.38461538461538464</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="67">
         <v>5</v>
       </c>
     </row>
@@ -3417,6 +3429,30 @@
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="77">
+        <v>46159</v>
+      </c>
+      <c r="F14" s="77">
+        <v>46180</v>
+      </c>
+      <c r="G14" s="17">
+        <f>F14-E14</f>
+        <v>21</v>
+      </c>
+      <c r="H14" s="76">
+        <v>12</v>
+      </c>
     </row>
     <row r="16" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
@@ -3568,11 +3604,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3600,11 +3636,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46159</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE80E6F-E6BB-4249-82C0-2759B19EDC48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B1B971-19F1-4C4C-A053-5F493A292F1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>HOJE</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>Flávia</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>Diana</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1082,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1353,11 +1359,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1460,18 +1466,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.9772727272727272E-2</v>
+        <v>3.8674033149171269E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1571,18 +1577,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.3380782918149468E-2</v>
+        <v>5.1546391752577317E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1645,7 +1651,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-249</v>
+        <v>-259</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1680,7 +1686,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-249</v>
+        <v>-259</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1735,18 +1741,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.1764705882352941E-2</v>
+        <v>1.1320754716981131E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1767,7 +1773,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1798,18 +1804,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1764705882352941E-2</v>
+        <v>1.1320754716981131E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1830,18 +1836,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.1764705882352941E-2</v>
+        <v>1.1320754716981131E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2182,14 +2188,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2214,14 +2220,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2246,14 +2252,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2278,14 +2284,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2344,18 +2350,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2379,18 +2385,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2414,18 +2420,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2497,14 +2503,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2722,14 +2728,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2756,14 +2762,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2790,14 +2796,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2824,14 +2830,14 @@
       </c>
       <c r="E6" s="71">
         <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2858,14 +2864,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2892,14 +2898,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2926,14 +2932,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f ca="1">E9-F9</f>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2960,14 +2966,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -2994,14 +3000,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3022,14 +3028,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3089,7 +3095,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3111,7 +3117,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3454,72 +3460,65 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="30" t="s">
+    <row r="15" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="77">
+        <v>46169</v>
+      </c>
+      <c r="F15" s="77">
+        <v>46190</v>
+      </c>
+      <c r="G15" s="17">
+        <f>F15-E15</f>
+        <v>21</v>
+      </c>
+      <c r="H15" s="76">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B17" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C17" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D17" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E17" s="31">
         <v>45996</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="I16" s="32"/>
-    </row>
-    <row r="18" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="59"/>
-      <c r="B18" s="62" t="s">
+      <c r="F17" s="31"/>
+      <c r="I17" s="32"/>
+    </row>
+    <row r="19" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="59"/>
+      <c r="B19" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C19" s="62" t="s">
         <v>81</v>
-      </c>
-      <c r="D18" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F18" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G18" s="62">
-        <f>F18-E18</f>
-        <v>21</v>
-      </c>
-      <c r="H18" s="62">
-        <v>12</v>
-      </c>
-      <c r="I18" s="64">
-        <f>J18/H18</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J18" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="62" t="s">
-        <v>8</v>
       </c>
       <c r="D19" s="62" t="s">
         <v>29</v>
       </c>
       <c r="E19" s="63">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F19" s="63">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G19" s="62">
         <f>F19-E19</f>
@@ -3530,9 +3529,40 @@
       </c>
       <c r="I19" s="64">
         <f>J19/H19</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J19" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F20" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G20" s="62">
+        <f>F20-E20</f>
+        <v>21</v>
+      </c>
+      <c r="H20" s="62">
+        <v>12</v>
+      </c>
+      <c r="I20" s="64">
+        <f>J20/H20</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J19" s="62">
+      <c r="J20" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3604,11 +3634,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3636,11 +3666,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B1B971-19F1-4C4C-A053-5F493A292F1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873D127B-EDB9-40CD-A284-4FF2F42600AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="93">
   <si>
     <t>HOJE</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Diana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caxuxa comeu os ovos </t>
   </si>
 </sst>
 </file>
@@ -316,7 +319,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,8 +425,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +443,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -745,6 +761,18 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1082,7 +1110,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1359,11 +1387,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1466,18 +1494,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.8674033149171269E-2</v>
+        <v>3.8461538461538464E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1577,18 +1605,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.1546391752577317E-2</v>
+        <v>5.1194539249146756E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1651,7 +1679,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-259</v>
+        <v>-261</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1686,7 +1714,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-259</v>
+        <v>-261</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1741,18 +1769,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.1320754716981131E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1773,7 +1801,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1804,18 +1832,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1320754716981131E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1836,18 +1864,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.1320754716981131E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2188,14 +2216,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2220,14 +2248,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2252,14 +2280,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2284,14 +2312,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2350,18 +2378,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2385,18 +2413,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2420,18 +2448,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2503,14 +2531,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2667,7 +2695,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2728,14 +2756,14 @@
       </c>
       <c r="E3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F3" s="68">
         <v>45947</v>
       </c>
       <c r="G3" s="67">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H3" s="67" t="s">
         <v>54</v>
@@ -2762,14 +2790,14 @@
       </c>
       <c r="E4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F4" s="68">
         <v>45953</v>
       </c>
       <c r="G4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H4" s="67" t="s">
         <v>54</v>
@@ -2796,14 +2824,14 @@
       </c>
       <c r="E5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F5" s="68">
         <v>45956</v>
       </c>
       <c r="G5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H5" s="67" t="s">
         <v>54</v>
@@ -2830,14 +2858,14 @@
       </c>
       <c r="E6" s="71">
         <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F6" s="71">
         <v>45910</v>
       </c>
       <c r="G6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H6" s="70" t="s">
         <v>54</v>
@@ -2864,14 +2892,14 @@
       </c>
       <c r="E7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F7" s="68">
         <v>46027</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H7" s="67" t="s">
         <v>54</v>
@@ -2898,14 +2926,14 @@
       </c>
       <c r="E8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F8" s="75">
         <v>46036</v>
       </c>
       <c r="G8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H8" s="74" t="s">
         <v>54</v>
@@ -2932,14 +2960,14 @@
       </c>
       <c r="E9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F9" s="18">
         <v>46082</v>
       </c>
       <c r="G9" s="17">
         <f ca="1">E9-F9</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>54</v>
@@ -2966,14 +2994,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -3000,14 +3028,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F11" s="73">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" s="72">
         <v>13</v>
@@ -3028,14 +3056,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F12" s="73">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H12" s="72">
         <v>13</v>
@@ -3095,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3117,7 +3145,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3460,96 +3488,92 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="76" t="s">
+    <row r="15" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="79">
         <v>46169</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="79">
         <v>46190</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="80">
         <f>F15-E15</f>
         <v>21</v>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="78">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30" t="s">
+      <c r="I15" s="81" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="77">
+        <v>46171</v>
+      </c>
+      <c r="F16" s="77">
+        <v>46192</v>
+      </c>
+      <c r="G16" s="17">
+        <f>F16-E16</f>
+        <v>21</v>
+      </c>
+      <c r="H16" s="76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B18" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C18" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D18" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E18" s="31">
         <v>45996</v>
       </c>
-      <c r="F17" s="31"/>
-      <c r="I17" s="32"/>
-    </row>
-    <row r="19" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59"/>
-      <c r="B19" s="62" t="s">
+      <c r="F18" s="31"/>
+      <c r="I18" s="32"/>
+    </row>
+    <row r="20" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="59"/>
+      <c r="B20" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C20" s="62" t="s">
         <v>81</v>
-      </c>
-      <c r="D19" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F19" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G19" s="62">
-        <f>F19-E19</f>
-        <v>21</v>
-      </c>
-      <c r="H19" s="62">
-        <v>12</v>
-      </c>
-      <c r="I19" s="64">
-        <f>J19/H19</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J19" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="62" t="s">
-        <v>8</v>
       </c>
       <c r="D20" s="62" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="63">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F20" s="63">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G20" s="62">
         <f>F20-E20</f>
@@ -3560,9 +3584,40 @@
       </c>
       <c r="I20" s="64">
         <f>J20/H20</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J20" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F21" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G21" s="62">
+        <f>F21-E21</f>
+        <v>21</v>
+      </c>
+      <c r="H21" s="62">
+        <v>12</v>
+      </c>
+      <c r="I21" s="64">
+        <f>J21/H21</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J21" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3634,11 +3689,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3666,11 +3721,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873D127B-EDB9-40CD-A284-4FF2F42600AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576F7F61-9282-4D8A-8F4F-2A023A5C82E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="93">
   <si>
     <t>HOJE</t>
   </si>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1387,11 +1387,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1494,18 +1494,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.8461538461538464E-2</v>
+        <v>3.7333333333333336E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1605,18 +1605,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>5.1194539249146756E-2</v>
+        <v>4.9342105263157895E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-261</v>
+        <v>-272</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-261</v>
+        <v>-272</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1769,18 +1769,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.1235955056179775E-2</v>
+        <v>1.0791366906474821E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1832,18 +1832,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1235955056179775E-2</v>
+        <v>1.0791366906474821E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1864,18 +1864,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.1235955056179775E-2</v>
+        <v>1.0791366906474821E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2216,14 +2216,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2248,14 +2248,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2280,14 +2280,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2312,14 +2312,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2378,18 +2378,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>724</v>
+        <v>746</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2413,18 +2413,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2448,18 +2448,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2531,14 +2531,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2675,73 +2675,75 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.7265625" style="47"/>
-    <col min="3" max="3" width="17.453125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" style="47"/>
-    <col min="5" max="5" width="10.7265625" style="48"/>
-    <col min="6" max="6" width="14.7265625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" style="47"/>
-    <col min="8" max="8" width="15.1796875" style="47" customWidth="1"/>
-    <col min="9" max="9" width="13.81640625" style="47" customWidth="1"/>
-    <col min="10" max="16384" width="10.7265625" style="47"/>
+    <col min="1" max="3" width="10.7265625" style="47"/>
+    <col min="4" max="4" width="17.453125" style="47" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="47"/>
+    <col min="6" max="6" width="10.7265625" style="48"/>
+    <col min="7" max="7" width="14.7265625" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" style="47"/>
+    <col min="9" max="9" width="15.1796875" style="47" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="10.7265625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="E1" s="46"/>
+        <v>46182</v>
+      </c>
       <c r="F1" s="46"/>
-      <c r="G1" s="49">
-        <f>SUM(J7:J10)</f>
-        <v>14</v>
-      </c>
-      <c r="H1" s="49" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="49">
+        <f>SUM(K7:K10)</f>
+        <v>13</v>
+      </c>
+      <c r="I1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="58"/>
       <c r="J1" s="58"/>
-    </row>
-    <row r="2" spans="1:10" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K1" s="58"/>
+    </row>
+    <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
       <c r="B2" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="F2" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="G2" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="H2" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="I2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="J2" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="K2" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="67" t="s">
         <v>18</v>
       </c>
@@ -2749,33 +2751,36 @@
         <v>6</v>
       </c>
       <c r="C3" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="E3" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="68">
+      <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="F3" s="68">
+        <v>46182</v>
+      </c>
+      <c r="G3" s="68">
         <v>45947</v>
       </c>
-      <c r="G3" s="67">
-        <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>224</v>
-      </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="67">
+        <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
+        <v>235</v>
+      </c>
+      <c r="I3" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="67">
+      <c r="J3" s="67">
         <v>4</v>
       </c>
-      <c r="J3" s="67">
+      <c r="K3" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -2783,33 +2788,36 @@
         <v>57</v>
       </c>
       <c r="C4" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="67" t="s">
+      <c r="E4" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="68">
+      <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="F4" s="68">
+        <v>46182</v>
+      </c>
+      <c r="G4" s="68">
         <v>45953</v>
       </c>
-      <c r="G4" s="67">
+      <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>218</v>
-      </c>
-      <c r="H4" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="I4" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="67">
+      <c r="J4" s="67">
         <v>8</v>
       </c>
-      <c r="J4" s="67">
+      <c r="K4" s="67">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
@@ -2817,33 +2825,36 @@
         <v>7</v>
       </c>
       <c r="C5" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="E5" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="68">
+      <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="F5" s="68">
+        <v>46182</v>
+      </c>
+      <c r="G5" s="68">
         <v>45956</v>
       </c>
-      <c r="G5" s="67">
+      <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>215</v>
-      </c>
-      <c r="H5" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="67">
+      <c r="J5" s="67">
         <v>8</v>
       </c>
-      <c r="J5" s="67">
+      <c r="K5" s="67">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="70" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="70" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
         <v>18</v>
       </c>
@@ -2851,33 +2862,36 @@
         <v>4</v>
       </c>
       <c r="C6" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="E6" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="71">
-        <f t="shared" ref="E6:E12" ca="1" si="1">TODAY()</f>
-        <v>46171</v>
-      </c>
       <c r="F6" s="71">
+        <f t="shared" ref="F6:F13" ca="1" si="1">TODAY()</f>
+        <v>46182</v>
+      </c>
+      <c r="G6" s="71">
         <v>45910</v>
       </c>
-      <c r="G6" s="70">
+      <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>261</v>
-      </c>
-      <c r="H6" s="70" t="s">
+        <v>272</v>
+      </c>
+      <c r="I6" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="70">
+      <c r="J6" s="70">
         <v>6</v>
       </c>
-      <c r="J6" s="70">
+      <c r="K6" s="70">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="67" t="s">
         <v>18</v>
       </c>
@@ -2885,33 +2899,36 @@
         <v>6</v>
       </c>
       <c r="C7" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="E7" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="68">
+      <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="F7" s="68">
+        <v>46182</v>
+      </c>
+      <c r="G7" s="68">
         <v>46027</v>
       </c>
-      <c r="G7" s="67">
+      <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>144</v>
-      </c>
-      <c r="H7" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="67">
+      <c r="J7" s="67">
         <v>7</v>
       </c>
-      <c r="J7" s="67">
+      <c r="K7" s="67">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="74" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="74" t="s">
         <v>18</v>
       </c>
@@ -2919,33 +2936,36 @@
         <v>9</v>
       </c>
       <c r="C8" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="E8" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="75">
+      <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="F8" s="75">
+        <v>46182</v>
+      </c>
+      <c r="G8" s="75">
         <v>46036</v>
       </c>
-      <c r="G8" s="74">
+      <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>135</v>
-      </c>
-      <c r="H8" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="74">
+      <c r="J8" s="74">
         <v>9</v>
       </c>
-      <c r="J8" s="74">
+      <c r="K8" s="74">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2953,33 +2973,36 @@
         <v>80</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="18">
+      <c r="F9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46171</v>
-      </c>
-      <c r="F9" s="18">
+        <v>46182</v>
+      </c>
+      <c r="G9" s="18">
         <v>46082</v>
       </c>
-      <c r="G9" s="17">
-        <f ca="1">E9-F9</f>
-        <v>89</v>
-      </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="17">
+        <f ca="1">F9-G9</f>
+        <v>100</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="17">
+      <c r="J9" s="17">
         <v>10</v>
       </c>
-      <c r="J9" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K9" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -2987,33 +3010,36 @@
         <v>7</v>
       </c>
       <c r="C10" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="18">
+      <c r="F10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46171</v>
-      </c>
-      <c r="F10" s="18">
+        <v>46182</v>
+      </c>
+      <c r="G10" s="18">
         <v>46089</v>
       </c>
-      <c r="G10" s="17">
-        <f t="shared" ref="G10:G12" ca="1" si="2">E10-F10</f>
-        <v>82</v>
-      </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="17">
+        <f t="shared" ref="H10:H12" ca="1" si="2">F10-G10</f>
+        <v>93</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="17">
+      <c r="J10" s="17">
         <v>10</v>
       </c>
-      <c r="J10" s="17">
+      <c r="K10" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="72" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="72" t="s">
         <v>17</v>
       </c>
@@ -3021,99 +3047,131 @@
         <v>6</v>
       </c>
       <c r="C11" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="E11" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="18">
+      <c r="F11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46171</v>
-      </c>
-      <c r="F11" s="73">
+        <v>46182</v>
+      </c>
+      <c r="G11" s="73">
         <v>46129</v>
       </c>
-      <c r="G11" s="17">
+      <c r="H11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="H11" s="72">
+        <v>53</v>
+      </c>
+      <c r="I11" s="72">
         <v>13</v>
-      </c>
-      <c r="I11" s="72">
-        <v>8</v>
       </c>
       <c r="J11" s="72">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="72">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C12" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="E12" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="18">
+      <c r="F12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>46171</v>
-      </c>
-      <c r="F12" s="73">
+        <v>46182</v>
+      </c>
+      <c r="G12" s="73">
         <v>46129</v>
       </c>
-      <c r="G12" s="17">
+      <c r="H12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="H12" s="72">
+        <v>53</v>
+      </c>
+      <c r="I12" s="72">
         <v>13</v>
-      </c>
-      <c r="I12" s="72">
-        <v>3</v>
       </c>
       <c r="J12" s="72">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="16"/>
-      <c r="F13" s="18"/>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E14" s="16"/>
-      <c r="F14" s="18"/>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E15" s="18"/>
+      <c r="K12" s="72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>46182</v>
+      </c>
+      <c r="G13" s="73">
+        <v>46182</v>
+      </c>
+      <c r="H13" s="17">
+        <f ca="1">G13-F13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="72">
+        <v>4</v>
+      </c>
+      <c r="K13" s="72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="16"/>
+      <c r="G14" s="18"/>
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="D16" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="E16" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="31">
+      <c r="F16" s="31">
         <v>45997</v>
       </c>
-      <c r="H16" s="32"/>
-    </row>
-    <row r="19" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F19" s="18"/>
-      <c r="G19" s="17"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="19" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G19" s="18"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="23"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3145,7 +3203,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3464,28 +3522,35 @@
       <c r="F13" s="16"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="76" t="s">
+    <row r="14" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="16">
         <v>46159</v>
       </c>
-      <c r="F14" s="77">
-        <v>46180</v>
-      </c>
-      <c r="G14" s="17">
+      <c r="F14" s="16">
+        <v>46182</v>
+      </c>
+      <c r="G14" s="15">
         <f>F14-E14</f>
-        <v>21</v>
-      </c>
-      <c r="H14" s="76">
+        <v>23</v>
+      </c>
+      <c r="H14" s="15">
         <v>12</v>
+      </c>
+      <c r="I14" s="33">
+        <f t="shared" ref="I13:I14" si="0">J14/H14</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J14" s="15">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.35">
@@ -3689,11 +3754,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3721,11 +3786,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576F7F61-9282-4D8A-8F4F-2A023A5C82E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE88A96F-6FFF-46D4-93BB-330B0FC76130}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="94">
   <si>
     <t>HOJE</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t xml:space="preserve">Caxuxa comeu os ovos </t>
+  </si>
+  <si>
+    <t>% vivos/nascidos</t>
   </si>
 </sst>
 </file>
@@ -529,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -773,6 +776,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1110,7 +1119,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1387,11 +1396,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1494,18 +1503,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.7333333333333336E-2</v>
+        <v>3.7135278514588858E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1605,18 +1614,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.9342105263157895E-2</v>
+        <v>4.9019607843137254E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1679,7 +1688,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-272</v>
+        <v>-274</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1714,7 +1723,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-272</v>
+        <v>-274</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1769,18 +1778,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.0791366906474821E-2</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1801,7 +1810,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1832,18 +1841,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.0791366906474821E-2</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1864,18 +1873,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.0791366906474821E-2</v>
+        <v>1.0714285714285714E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2216,14 +2225,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2248,14 +2257,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2280,14 +2289,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2312,14 +2321,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2378,18 +2387,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2413,18 +2422,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2448,18 +2457,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2531,14 +2540,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2675,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="10.7265625" style="47"/>
@@ -2689,14 +2698,14 @@
     <col min="11" max="16384" width="10.7265625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2710,7 +2719,7 @@
       <c r="J1" s="58"/>
       <c r="K1" s="58"/>
     </row>
-    <row r="2" spans="1:11" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2742,8 +2751,11 @@
       <c r="K2" s="50" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="83" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="67" t="s">
         <v>18</v>
       </c>
@@ -2761,14 +2773,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2779,8 +2791,12 @@
       <c r="K3" s="67">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="69">
+        <f>K3/J3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -2798,14 +2814,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2816,8 +2832,12 @@
       <c r="K4" s="67">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="69">
+        <f t="shared" ref="L4:L14" si="1">K4/J4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
@@ -2835,14 +2855,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2850,11 +2870,16 @@
       <c r="J5" s="67">
         <v>8</v>
       </c>
-      <c r="K5" s="67">
+      <c r="K5" s="74">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="82">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="74"/>
+    </row>
+    <row r="6" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
         <v>18</v>
       </c>
@@ -2871,15 +2896,15 @@
         <v>30</v>
       </c>
       <c r="F6" s="71">
-        <f t="shared" ref="F6:F13" ca="1" si="1">TODAY()</f>
-        <v>46182</v>
+        <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
+        <v>46184</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2887,11 +2912,16 @@
       <c r="J6" s="70">
         <v>6</v>
       </c>
-      <c r="K6" s="70">
+      <c r="K6" s="67">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="69">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M6" s="67"/>
+    </row>
+    <row r="7" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="67" t="s">
         <v>18</v>
       </c>
@@ -2909,14 +2939,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2927,8 +2957,12 @@
       <c r="K7" s="67">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" s="74" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L7" s="69">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="74" t="s">
         <v>18</v>
       </c>
@@ -2946,14 +2980,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -2964,8 +2998,12 @@
       <c r="K8" s="74">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="82">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2982,15 +3020,15 @@
         <v>29</v>
       </c>
       <c r="F9" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3001,8 +3039,12 @@
       <c r="K9" s="17">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="22">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -3019,15 +3061,15 @@
         <v>29</v>
       </c>
       <c r="F10" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
-        <f t="shared" ref="H10:H12" ca="1" si="2">F10-G10</f>
-        <v>93</v>
+        <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
+        <v>95</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3038,8 +3080,12 @@
       <c r="K10" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="22">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="72" t="s">
         <v>17</v>
       </c>
@@ -3056,18 +3102,18 @@
         <v>29</v>
       </c>
       <c r="F11" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>53</v>
-      </c>
-      <c r="I11" s="72">
-        <v>13</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="J11" s="72">
         <v>8</v>
@@ -3075,8 +3121,12 @@
       <c r="K11" s="72">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L11" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C12" s="72" t="s">
         <v>84</v>
       </c>
@@ -3087,18 +3137,18 @@
         <v>34</v>
       </c>
       <c r="F12" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>53</v>
-      </c>
-      <c r="I12" s="72">
-        <v>13</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="J12" s="72">
         <v>3</v>
@@ -3106,8 +3156,12 @@
       <c r="K12" s="72">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" s="72" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C13" s="72" t="s">
         <v>88</v>
       </c>
@@ -3118,15 +3172,15 @@
         <v>29</v>
       </c>
       <c r="F13" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3135,19 +3189,54 @@
         <v>4</v>
       </c>
       <c r="K13" s="72">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
-      <c r="J14" s="33"/>
-    </row>
-    <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="L13" s="22">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="18">
+        <f t="shared" ca="1" si="2"/>
+        <v>46184</v>
+      </c>
+      <c r="G14" s="77">
+        <v>46184</v>
+      </c>
+      <c r="H14" s="17">
+        <f ca="1">G14-F14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="72">
+        <v>1</v>
+      </c>
+      <c r="K14" s="72">
+        <v>1</v>
+      </c>
+      <c r="L14" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M14" s="17"/>
+    </row>
+    <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
     </row>
-    <row r="16" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
         <v>35</v>
       </c>
@@ -3203,7 +3292,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3546,7 +3635,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="33">
-        <f t="shared" ref="I13:I14" si="0">J14/H14</f>
+        <f>J14/H14</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="J14" s="15">
@@ -3594,14 +3683,21 @@
         <v>46171</v>
       </c>
       <c r="F16" s="77">
-        <v>46192</v>
+        <v>46184</v>
       </c>
       <c r="G16" s="17">
         <f>F16-E16</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H16" s="76">
         <v>3</v>
+      </c>
+      <c r="I16" s="33">
+        <f>J16/H16</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J16" s="76">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
@@ -3754,11 +3850,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3786,11 +3882,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE88A96F-6FFF-46D4-93BB-330B0FC76130}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA504E-31E0-4D37-AC73-753FB9E1FA7B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="94">
   <si>
     <t>HOJE</t>
   </si>
@@ -436,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,12 +446,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,23 +759,23 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1119,7 +1113,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1396,11 +1390,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1503,18 +1497,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.7135278514588858E-2</v>
+        <v>3.6745406824146981E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1614,18 +1608,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.9019607843137254E-2</v>
+        <v>4.8387096774193547E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1688,7 +1682,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-274</v>
+        <v>-278</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1723,7 +1717,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-274</v>
+        <v>-278</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1778,18 +1772,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.0714285714285714E-2</v>
+        <v>1.0563380281690141E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1810,7 +1804,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1841,18 +1835,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.0714285714285714E-2</v>
+        <v>1.0563380281690141E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1873,18 +1867,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.0714285714285714E-2</v>
+        <v>1.0563380281690141E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2225,14 +2219,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,14 +2251,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,14 +2283,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,14 +2315,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2387,18 +2381,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2422,18 +2416,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2457,18 +2451,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2540,14 +2534,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2705,7 +2699,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2751,7 +2745,7 @@
       <c r="K2" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L2" s="83" t="s">
+      <c r="L2" s="79" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2773,14 +2767,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2814,14 +2808,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2855,14 +2849,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2873,7 +2867,7 @@
       <c r="K5" s="74">
         <v>4</v>
       </c>
-      <c r="L5" s="82">
+      <c r="L5" s="78">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -2897,14 +2891,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2939,14 +2933,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2980,14 +2974,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -2998,7 +2992,7 @@
       <c r="K8" s="74">
         <v>3</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="78">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
@@ -3021,14 +3015,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3062,14 +3056,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3103,14 +3097,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,14 +3132,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3173,14 +3167,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3208,14 +3202,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3270,7 +3264,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3292,7 +3286,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3611,174 +3605,212 @@
       <c r="F13" s="16"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
+    <row r="14" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="81">
         <v>46159</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="81">
         <v>46182</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="82">
         <f>F14-E14</f>
         <v>23</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="80">
         <v>12</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="83">
         <f>J14/H14</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="80">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="78" t="s">
+    <row r="15" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="78" t="s">
+      <c r="D15" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="79">
+      <c r="E15" s="81">
         <v>46169</v>
       </c>
-      <c r="F15" s="79">
+      <c r="F15" s="81">
         <v>46190</v>
       </c>
-      <c r="G15" s="80">
+      <c r="G15" s="82">
         <f>F15-E15</f>
         <v>21</v>
       </c>
-      <c r="H15" s="78">
+      <c r="H15" s="80">
         <v>12</v>
       </c>
-      <c r="I15" s="81" t="s">
+      <c r="I15" s="83" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="76" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="76" t="s">
+    <row r="16" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="77">
+      <c r="E16" s="81">
         <v>46171</v>
       </c>
-      <c r="F16" s="77">
+      <c r="F16" s="81">
         <v>46184</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="82">
         <f>F16-E16</f>
         <v>13</v>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="80">
         <v>3</v>
       </c>
-      <c r="I16" s="33">
+      <c r="I16" s="83">
         <f>J16/H16</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J16" s="76">
+      <c r="J16" s="80">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+    <row r="17" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="17"/>
+      <c r="I17" s="33"/>
+    </row>
+    <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="18">
+        <v>46188</v>
+      </c>
+      <c r="F18" s="18">
+        <v>46209</v>
+      </c>
+      <c r="G18" s="17">
+        <f>F18-E18</f>
+        <v>21</v>
+      </c>
+      <c r="H18" s="17">
+        <v>14</v>
+      </c>
+      <c r="I18" s="22">
+        <f>J18/H18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="22"/>
+    </row>
+    <row r="20" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B20" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C20" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D20" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E20" s="31">
         <v>45996</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="I18" s="32"/>
-    </row>
-    <row r="20" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="59"/>
-      <c r="B20" s="62" t="s">
+      <c r="F20" s="31"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="22" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="59"/>
+      <c r="B22" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C22" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="62" t="s">
+      <c r="D22" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E22" s="63">
         <v>46060</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F22" s="63">
         <v>46081</v>
       </c>
-      <c r="G20" s="62">
-        <f>F20-E20</f>
+      <c r="G22" s="62">
+        <f>F22-E22</f>
         <v>21</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H22" s="62">
         <v>12</v>
       </c>
-      <c r="I20" s="64">
-        <f>J20/H20</f>
+      <c r="I22" s="64">
+        <f>J22/H22</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J22" s="62">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="62" t="s">
+    <row r="23" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="D23" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="63">
+      <c r="E23" s="63">
         <v>46067</v>
       </c>
-      <c r="F21" s="63">
+      <c r="F23" s="63">
         <v>46088</v>
       </c>
-      <c r="G21" s="62">
-        <f>F21-E21</f>
+      <c r="G23" s="62">
+        <f>F23-E23</f>
         <v>21</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H23" s="62">
         <v>12</v>
       </c>
-      <c r="I21" s="64">
-        <f>J21/H21</f>
+      <c r="I23" s="64">
+        <f>J23/H23</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J21" s="62">
+      <c r="J23" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3850,11 +3882,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3882,11 +3914,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA504E-31E0-4D37-AC73-753FB9E1FA7B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5483504-FA4B-4748-A83F-69FC5F49C3FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="95">
   <si>
     <t>HOJE</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>% vivos/nascidos</t>
+  </si>
+  <si>
+    <t>Miuda</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1116,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1390,11 +1393,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1497,18 +1500,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6745406824146981E-2</v>
+        <v>3.608247422680412E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1608,18 +1611,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.8387096774193547E-2</v>
+        <v>4.7318611987381701E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1682,7 +1685,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-278</v>
+        <v>-285</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1717,7 +1720,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-278</v>
+        <v>-285</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1772,18 +1775,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.0563380281690141E-2</v>
+        <v>1.0309278350515464E-2</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1804,7 +1807,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1835,18 +1838,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.0563380281690141E-2</v>
+        <v>1.0309278350515464E-2</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1867,18 +1870,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.0563380281690141E-2</v>
+        <v>1.0309278350515464E-2</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2219,14 +2222,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2251,14 +2254,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2283,14 +2286,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2315,14 +2318,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2381,18 +2384,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2416,18 +2419,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2451,18 +2454,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2534,14 +2537,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2699,7 +2702,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2767,14 +2770,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2808,14 +2811,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2849,14 +2852,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2891,14 +2894,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2933,14 +2936,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2974,14 +2977,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3015,14 +3018,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3056,14 +3059,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3097,14 +3100,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3132,14 +3135,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3167,14 +3170,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3202,14 +3205,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3264,7 +3267,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3286,7 +3289,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3732,72 +3735,73 @@
       </c>
       <c r="K18" s="22"/>
     </row>
-    <row r="20" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="30" t="s">
+    <row r="19" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="18">
+        <v>46194</v>
+      </c>
+      <c r="F19" s="18">
+        <v>46215</v>
+      </c>
+      <c r="G19" s="17">
+        <f>F19-E19</f>
+        <v>21</v>
+      </c>
+      <c r="H19" s="17">
+        <v>12</v>
+      </c>
+      <c r="I19" s="22">
+        <f>J19/H19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="22"/>
+    </row>
+    <row r="21" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B21" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C21" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D21" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E21" s="31">
         <v>45996</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="I20" s="32"/>
-    </row>
-    <row r="22" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="59"/>
-      <c r="B22" s="62" t="s">
+      <c r="F21" s="31"/>
+      <c r="I21" s="32"/>
+    </row>
+    <row r="23" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="59"/>
+      <c r="B23" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C23" s="62" t="s">
         <v>81</v>
-      </c>
-      <c r="D22" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F22" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G22" s="62">
-        <f>F22-E22</f>
-        <v>21</v>
-      </c>
-      <c r="H22" s="62">
-        <v>12</v>
-      </c>
-      <c r="I22" s="64">
-        <f>J22/H22</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J22" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="62" t="s">
-        <v>8</v>
       </c>
       <c r="D23" s="62" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="63">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F23" s="63">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G23" s="62">
         <f>F23-E23</f>
@@ -3808,9 +3812,40 @@
       </c>
       <c r="I23" s="64">
         <f>J23/H23</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J23" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F24" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G24" s="62">
+        <f>F24-E24</f>
+        <v>21</v>
+      </c>
+      <c r="H24" s="62">
+        <v>12</v>
+      </c>
+      <c r="I24" s="64">
+        <f>J24/H24</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J24" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3882,11 +3917,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3914,11 +3949,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5483504-FA4B-4748-A83F-69FC5F49C3FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A845B6EE-1349-4704-A535-F7CD24590727}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="96">
   <si>
     <t>HOJE</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>Miuda</t>
+  </si>
+  <si>
+    <t>MI</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1119,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1393,11 +1396,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1500,18 +1503,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.608247422680412E-2</v>
+        <v>3.4229828850855744E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1611,18 +1614,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.7318611987381701E-2</v>
+        <v>4.4378698224852069E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1685,7 +1688,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-285</v>
+        <v>-306</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1720,7 +1723,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-285</v>
+        <v>-306</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1775,18 +1778,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>1.0309278350515464E-2</v>
+        <v>9.6153846153846159E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1807,7 +1810,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1838,18 +1841,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.0309278350515464E-2</v>
+        <v>9.6153846153846159E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1870,18 +1873,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>1.0309278350515464E-2</v>
+        <v>9.6153846153846159E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2222,14 +2225,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2254,14 +2257,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2286,14 +2289,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2318,14 +2321,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2384,18 +2387,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2419,18 +2422,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2454,18 +2457,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2537,14 +2540,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2681,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="10.7265625" style="47"/>
@@ -2702,7 +2705,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2770,14 +2773,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2811,14 +2814,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2852,14 +2855,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2894,14 +2897,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2936,14 +2939,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2977,14 +2980,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3018,14 +3021,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3059,14 +3062,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3100,14 +3103,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3135,14 +3138,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3170,14 +3173,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-13</v>
+        <v>-34</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3205,14 +3208,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-11</v>
+        <v>-32</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3230,34 +3233,102 @@
       <c r="M14" s="17"/>
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="30" t="s">
+      <c r="C15" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46216</v>
+      </c>
+      <c r="G15" s="18">
+        <v>46216</v>
+      </c>
+      <c r="H15" s="17">
+        <f ca="1">F15-G15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="72">
+        <v>8</v>
+      </c>
+      <c r="K15" s="72">
+        <v>8</v>
+      </c>
+      <c r="L15" s="22">
+        <f>K15/J15</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="22"/>
+    </row>
+    <row r="18" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="17"/>
+    </row>
+    <row r="20" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B20" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D20" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E20" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F20" s="31">
         <v>45997</v>
       </c>
-      <c r="I16" s="32"/>
-    </row>
-    <row r="19" spans="7:12" x14ac:dyDescent="0.35">
-      <c r="G19" s="18"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="23"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G23" s="18"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3289,7 +3360,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3727,11 +3798,14 @@
         <v>21</v>
       </c>
       <c r="H18" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I18" s="22">
         <f>J18/H18</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J18" s="17">
+        <v>12</v>
       </c>
       <c r="K18" s="22"/>
     </row>
@@ -3763,7 +3837,10 @@
       </c>
       <c r="I19" s="22">
         <f>J19/H19</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J19" s="17">
+        <v>8</v>
       </c>
       <c r="K19" s="22"/>
     </row>
@@ -3917,11 +3994,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -3949,11 +4026,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A845B6EE-1349-4704-A535-F7CD24590727}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E64AC3-9626-473B-A5C4-DCD21CE5CD02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
   <si>
     <t>HOJE</t>
   </si>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1503,18 +1503,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4229828850855744E-2</v>
+        <v>3.3734939759036145E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1614,18 +1614,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.4378698224852069E-2</v>
+        <v>4.3604651162790699E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-306</v>
+        <v>-312</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-306</v>
+        <v>-312</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1778,18 +1778,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>9.6153846153846159E-3</v>
+        <v>9.433962264150943E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1841,18 +1841,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>9.6153846153846159E-3</v>
+        <v>9.433962264150943E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1873,18 +1873,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>9.6153846153846159E-3</v>
+        <v>9.433962264150943E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2225,14 +2225,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,14 +2257,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,14 +2289,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,14 +2321,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2387,18 +2387,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2422,18 +2422,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2457,18 +2457,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2705,7 +2705,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2773,14 +2773,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2814,14 +2814,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2855,14 +2855,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2897,14 +2897,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,14 +3138,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-34</v>
+        <v>-40</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-32</v>
+        <v>-38</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3338,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3769,160 +3769,209 @@
       </c>
     </row>
     <row r="17" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="17"/>
-      <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17" t="s">
+      <c r="C17" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="81">
+        <v>46188</v>
+      </c>
+      <c r="F17" s="81">
+        <v>46209</v>
+      </c>
+      <c r="G17" s="82">
+        <f>F17-E17</f>
+        <v>21</v>
+      </c>
+      <c r="H17" s="80">
+        <v>12</v>
+      </c>
+      <c r="I17" s="83">
+        <f>J17/H17</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="80">
+        <v>12</v>
+      </c>
+      <c r="K17" s="80"/>
+    </row>
+    <row r="18" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="18">
-        <v>46188</v>
-      </c>
-      <c r="F18" s="18">
-        <v>46209</v>
-      </c>
-      <c r="G18" s="17">
+      <c r="C18" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="81">
+        <v>46194</v>
+      </c>
+      <c r="F18" s="81">
+        <v>46215</v>
+      </c>
+      <c r="G18" s="82">
         <f>F18-E18</f>
         <v>21</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="80">
         <v>12</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="83">
         <f>J18/H18</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J18" s="80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B20" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="18">
+        <v>46191</v>
+      </c>
+      <c r="F20" s="73">
+        <v>46212</v>
+      </c>
+      <c r="G20" s="17">
+        <f>F20-E20</f>
+        <v>21</v>
+      </c>
+      <c r="H20" s="17">
         <v>12</v>
       </c>
-      <c r="K18" s="22"/>
-    </row>
-    <row r="19" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="I20" s="22">
+        <f>J20/H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="22"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="22"/>
+    </row>
+    <row r="23" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="31">
+        <v>45996</v>
+      </c>
+      <c r="F23" s="31"/>
+      <c r="I23" s="32"/>
+    </row>
+    <row r="25" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="59"/>
+      <c r="B25" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="63">
+        <v>46060</v>
+      </c>
+      <c r="F25" s="63">
+        <v>46081</v>
+      </c>
+      <c r="G25" s="62">
+        <f>F25-E25</f>
+        <v>21</v>
+      </c>
+      <c r="H25" s="62">
+        <v>12</v>
+      </c>
+      <c r="I25" s="64">
+        <f>J25/H25</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J25" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="18">
-        <v>46194</v>
-      </c>
-      <c r="F19" s="18">
-        <v>46215</v>
-      </c>
-      <c r="G19" s="17">
-        <f>F19-E19</f>
+      <c r="C26" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F26" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G26" s="62">
+        <f>F26-E26</f>
         <v>21</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H26" s="62">
         <v>12</v>
       </c>
-      <c r="I19" s="22">
-        <f>J19/H19</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J19" s="17">
-        <v>8</v>
-      </c>
-      <c r="K19" s="22"/>
-    </row>
-    <row r="21" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="31">
-        <v>45996</v>
-      </c>
-      <c r="F21" s="31"/>
-      <c r="I21" s="32"/>
-    </row>
-    <row r="23" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="59"/>
-      <c r="B23" s="62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F23" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G23" s="62">
-        <f>F23-E23</f>
-        <v>21</v>
-      </c>
-      <c r="H23" s="62">
-        <v>12</v>
-      </c>
-      <c r="I23" s="64">
-        <f>J23/H23</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J23" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="63">
-        <v>46067</v>
-      </c>
-      <c r="F24" s="63">
-        <v>46088</v>
-      </c>
-      <c r="G24" s="62">
-        <f>F24-E24</f>
-        <v>21</v>
-      </c>
-      <c r="H24" s="62">
-        <v>12</v>
-      </c>
-      <c r="I24" s="64">
-        <f>J24/H24</f>
+      <c r="I26" s="64">
+        <f>J26/H26</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J24" s="62">
+      <c r="J26" s="62">
         <v>5</v>
       </c>
     </row>
@@ -3994,11 +4043,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4026,11 +4075,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46222</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E64AC3-9626-473B-A5C4-DCD21CE5CD02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689F7154-ADB5-45D8-9541-BC1556868EA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="96">
   <si>
     <t>HOJE</t>
   </si>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1503,18 +1503,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.3734939759036145E-2</v>
+        <v>3.3653846153846152E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1614,18 +1614,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.3604651162790699E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-312</v>
+        <v>-313</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-312</v>
+        <v>-313</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1778,18 +1778,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>9.433962264150943E-3</v>
+        <v>9.4043887147335428E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1841,18 +1841,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>9.433962264150943E-3</v>
+        <v>9.4043887147335428E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1873,18 +1873,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>9.433962264150943E-3</v>
+        <v>9.4043887147335428E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2225,14 +2225,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,14 +2257,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,14 +2289,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,14 +2321,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2387,18 +2387,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2422,18 +2422,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2457,18 +2457,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2705,7 +2705,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2773,14 +2773,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2814,14 +2814,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2855,14 +2855,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2897,14 +2897,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,14 +3138,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3338,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3850,10 +3850,10 @@
         <v>29</v>
       </c>
       <c r="E20" s="18">
-        <v>46191</v>
+        <v>46221</v>
       </c>
       <c r="F20" s="73">
-        <v>46212</v>
+        <v>46242</v>
       </c>
       <c r="G20" s="17">
         <f>F20-E20</f>
@@ -3870,15 +3870,33 @@
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
+      <c r="B21" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="18">
+        <v>46223</v>
+      </c>
+      <c r="F21" s="73">
+        <v>46244</v>
+      </c>
+      <c r="G21" s="17">
+        <f>F21-E21</f>
+        <v>21</v>
+      </c>
+      <c r="H21" s="17">
+        <v>12</v>
+      </c>
+      <c r="I21" s="22">
+        <f>J21/H21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="17"/>
       <c r="K21" s="22"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -3893,72 +3911,53 @@
       <c r="J22" s="72"/>
       <c r="K22" s="22"/>
     </row>
-    <row r="23" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="30" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="22"/>
+    </row>
+    <row r="24" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B24" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C24" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D24" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="31">
         <v>45996</v>
       </c>
-      <c r="F23" s="31"/>
-      <c r="I23" s="32"/>
-    </row>
-    <row r="25" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="59"/>
-      <c r="B25" s="62" t="s">
+      <c r="F24" s="31"/>
+      <c r="I24" s="32"/>
+    </row>
+    <row r="26" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="59"/>
+      <c r="B26" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C26" s="62" t="s">
         <v>81</v>
-      </c>
-      <c r="D25" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F25" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G25" s="62">
-        <f>F25-E25</f>
-        <v>21</v>
-      </c>
-      <c r="H25" s="62">
-        <v>12</v>
-      </c>
-      <c r="I25" s="64">
-        <f>J25/H25</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J25" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>8</v>
       </c>
       <c r="D26" s="62" t="s">
         <v>29</v>
       </c>
       <c r="E26" s="63">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F26" s="63">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G26" s="62">
         <f>F26-E26</f>
@@ -3969,9 +3968,40 @@
       </c>
       <c r="I26" s="64">
         <f>J26/H26</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J26" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F27" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G27" s="62">
+        <f>F27-E27</f>
+        <v>21</v>
+      </c>
+      <c r="H27" s="62">
+        <v>12</v>
+      </c>
+      <c r="I27" s="64">
+        <f>J27/H27</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J26" s="62">
+      <c r="J27" s="62">
         <v>5</v>
       </c>
     </row>
@@ -4043,11 +4073,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4075,11 +4105,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689F7154-ADB5-45D8-9541-BC1556868EA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826751B6-6754-4558-BCC0-629DC68381AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="96">
   <si>
     <t>HOJE</t>
   </si>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1503,18 +1503,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.3653846153846152E-2</v>
+        <v>3.2634032634032632E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1614,18 +1614,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.3478260869565216E-2</v>
+        <v>4.189944134078212E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-313</v>
+        <v>-326</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-313</v>
+        <v>-326</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1778,18 +1778,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>9.4043887147335428E-3</v>
+        <v>9.0361445783132526E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1841,18 +1841,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>9.4043887147335428E-3</v>
+        <v>9.0361445783132526E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1873,18 +1873,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>9.4043887147335428E-3</v>
+        <v>9.0361445783132526E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2225,14 +2225,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,14 +2257,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,14 +2289,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,14 +2321,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2387,18 +2387,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>828</v>
+        <v>854</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2422,18 +2422,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2457,18 +2457,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2705,7 +2705,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2773,14 +2773,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2814,14 +2814,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2855,14 +2855,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2897,14 +2897,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,14 +3138,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-41</v>
+        <v>-54</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-39</v>
+        <v>-52</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3900,9 +3900,15 @@
       <c r="K21" s="22"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
+      <c r="B22" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="72" t="s">
+        <v>34</v>
+      </c>
       <c r="E22" s="18"/>
       <c r="F22" s="73"/>
       <c r="G22" s="17"/>
@@ -4073,11 +4079,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4105,11 +4111,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826751B6-6754-4558-BCC0-629DC68381AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC447DEF-7C27-4FE2-B29F-1728DFB26134}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="98">
   <si>
     <t>HOJE</t>
   </si>
@@ -319,6 +319,12 @@
   </si>
   <si>
     <t>MI</t>
+  </si>
+  <si>
+    <t>JE</t>
+  </si>
+  <si>
+    <t>Jéssica</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1125,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1396,11 +1402,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1503,18 +1509,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.2634032634032632E-2</v>
+        <v>3.255813953488372E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1614,18 +1620,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.189944134078212E-2</v>
+        <v>4.1782729805013928E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1688,7 +1694,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-326</v>
+        <v>-327</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1723,7 +1729,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-326</v>
+        <v>-327</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1778,18 +1784,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>9.0361445783132526E-3</v>
+        <v>9.0090090090090089E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1810,7 +1816,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1841,18 +1847,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>9.0361445783132526E-3</v>
+        <v>9.0090090090090089E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1873,18 +1879,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>9.0361445783132526E-3</v>
+        <v>9.0090090090090089E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2225,14 +2231,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,14 +2263,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,14 +2295,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,14 +2327,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2387,18 +2393,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2422,18 +2428,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2457,18 +2463,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2540,14 +2546,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2705,7 +2711,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2773,14 +2779,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2814,14 +2820,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2855,14 +2861,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2897,14 +2903,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2939,14 +2945,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2980,14 +2986,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3021,14 +3027,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3062,14 +3068,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3103,14 +3109,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,14 +3144,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3173,14 +3179,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3208,14 +3214,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3244,14 +3250,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3338,7 +3344,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
@@ -3360,7 +3366,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3911,90 +3917,95 @@
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="73"/>
-      <c r="G22" s="17"/>
+      <c r="G22" s="17">
+        <f t="shared" ref="G22:G23" si="0">F22-E22</f>
+        <v>0</v>
+      </c>
       <c r="H22" s="17"/>
-      <c r="I22" s="72"/>
+      <c r="I22" s="22" t="e">
+        <f t="shared" ref="I22:I23" si="1">J22/H22</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J22" s="72"/>
       <c r="K22" s="22"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="72"/>
+      <c r="B23" s="72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="72" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="18">
+        <v>46237</v>
+      </c>
+      <c r="F23" s="73">
+        <v>46258</v>
+      </c>
+      <c r="G23" s="17">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="H23" s="17">
+        <v>10</v>
+      </c>
+      <c r="I23" s="22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="J23" s="72"/>
       <c r="K23" s="22"/>
     </row>
-    <row r="24" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="30" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="22"/>
+    </row>
+    <row r="25" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B25" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C25" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D25" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E25" s="31">
         <v>45996</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="I24" s="32"/>
-    </row>
-    <row r="26" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="59"/>
-      <c r="B26" s="62" t="s">
+      <c r="F25" s="31"/>
+      <c r="I25" s="32"/>
+    </row>
+    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="59"/>
+      <c r="B27" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C27" s="62" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="63">
-        <v>46060</v>
-      </c>
-      <c r="F26" s="63">
-        <v>46081</v>
-      </c>
-      <c r="G26" s="62">
-        <f>F26-E26</f>
-        <v>21</v>
-      </c>
-      <c r="H26" s="62">
-        <v>12</v>
-      </c>
-      <c r="I26" s="64">
-        <f>J26/H26</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J26" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>8</v>
       </c>
       <c r="D27" s="62" t="s">
         <v>29</v>
       </c>
       <c r="E27" s="63">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F27" s="63">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G27" s="62">
         <f>F27-E27</f>
@@ -4005,9 +4016,40 @@
       </c>
       <c r="I27" s="64">
         <f>J27/H27</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J27" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="63">
+        <v>46067</v>
+      </c>
+      <c r="F28" s="63">
+        <v>46088</v>
+      </c>
+      <c r="G28" s="62">
+        <f>F28-E28</f>
+        <v>21</v>
+      </c>
+      <c r="H28" s="62">
+        <v>12</v>
+      </c>
+      <c r="I28" s="64">
+        <f>J28/H28</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J27" s="62">
+      <c r="J28" s="62">
         <v>5</v>
       </c>
     </row>
@@ -4079,11 +4121,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4111,11 +4153,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC447DEF-7C27-4FE2-B29F-1728DFB26134}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91D0365-AFBC-45BC-B237-EF54ADFCDEEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="99">
   <si>
     <t>HOJE</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Jéssica</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -334,7 +337,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +450,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -538,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -788,6 +799,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1125,7 +1145,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1402,11 +1422,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1509,18 +1529,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.255813953488372E-2</v>
+        <v>3.1890660592255128E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1620,18 +1640,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.1782729805013928E-2</v>
+        <v>4.0760869565217392E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1694,7 +1714,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-327</v>
+        <v>-336</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1729,7 +1749,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-327</v>
+        <v>-336</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1784,18 +1804,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>9.0090090090090089E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1816,7 +1836,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1847,18 +1867,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>9.0090090090090089E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1879,18 +1899,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>9.0090090090090089E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2231,14 +2251,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2263,14 +2283,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2295,14 +2315,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2327,14 +2347,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2393,18 +2413,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>856</v>
+        <v>874</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2428,18 +2448,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2463,18 +2483,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2546,14 +2566,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2711,7 +2731,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2779,14 +2799,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2820,14 +2840,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2861,14 +2881,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2903,14 +2923,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2945,14 +2965,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2986,14 +3006,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3027,14 +3047,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3068,14 +3088,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3109,14 +3129,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3144,14 +3164,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3179,14 +3199,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-55</v>
+        <v>-64</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3214,14 +3234,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-53</v>
+        <v>-62</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3250,14 +3270,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3366,7 +3386,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3845,7 +3865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" s="85" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B20" s="72" t="s">
         <v>6</v>
       </c>
@@ -3855,27 +3875,29 @@
       <c r="D20" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="73">
         <v>46221</v>
       </c>
       <c r="F20" s="73">
-        <v>46242</v>
-      </c>
-      <c r="G20" s="17">
+        <v>46245</v>
+      </c>
+      <c r="G20" s="72">
         <f>F20-E20</f>
-        <v>21</v>
-      </c>
-      <c r="H20" s="17">
+        <v>24</v>
+      </c>
+      <c r="H20" s="72">
         <v>12</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="86">
         <f>J20/H20</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="22"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J20" s="72">
+        <v>11</v>
+      </c>
+      <c r="K20" s="86"/>
+    </row>
+    <row r="21" spans="1:11" s="85" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B21" s="72" t="s">
         <v>9</v>
       </c>
@@ -3885,78 +3907,86 @@
       <c r="D21" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="73">
         <v>46223</v>
       </c>
       <c r="F21" s="73">
-        <v>46244</v>
-      </c>
-      <c r="G21" s="17">
+        <v>46245</v>
+      </c>
+      <c r="G21" s="72">
         <f>F21-E21</f>
-        <v>21</v>
-      </c>
-      <c r="H21" s="17">
+        <v>22</v>
+      </c>
+      <c r="H21" s="72">
         <v>12</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="86">
         <f>J21/H21</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="22"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="72" t="s">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J21" s="72">
+        <v>7</v>
+      </c>
+      <c r="K21" s="86"/>
+    </row>
+    <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="D22" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="17">
-        <f t="shared" ref="G22:G23" si="0">F22-E22</f>
-        <v>0</v>
+      <c r="E22" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="18">
+        <f t="shared" ref="F21:F23" ca="1" si="0">TODAY()</f>
+        <v>46246</v>
+      </c>
+      <c r="G22" s="17" t="e">
+        <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="22" t="e">
-        <f t="shared" ref="I22:I23" si="1">J22/H22</f>
+        <f t="shared" ref="I22:I23" si="2">J22/H22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J22" s="72"/>
+      <c r="J22" s="17"/>
       <c r="K22" s="22"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B23" s="72" t="s">
+    <row r="23" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="D23" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="18">
         <v>46237</v>
       </c>
-      <c r="F23" s="73">
-        <v>46258</v>
+      <c r="F23" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>46246</v>
       </c>
       <c r="G23" s="17">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
       </c>
       <c r="H23" s="17">
         <v>10</v>
       </c>
       <c r="I23" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J23" s="72"/>
+      <c r="J23" s="17"/>
       <c r="K23" s="22"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -4121,11 +4151,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4153,11 +4183,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91D0365-AFBC-45BC-B237-EF54ADFCDEEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA29442-169B-4057-A99F-E926AA41346E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -337,7 +337,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,14 +450,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -549,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -802,12 +794,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,7 +1131,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1422,11 +1408,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1529,18 +1515,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.1890660592255128E-2</v>
+        <v>3.1319910514541388E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1640,18 +1626,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>4.0760869565217392E-2</v>
+        <v>3.9893617021276598E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1714,7 +1700,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-336</v>
+        <v>-344</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1749,7 +1735,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-336</v>
+        <v>-344</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1804,18 +1790,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5714285714285719E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1836,7 +1822,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1867,18 +1853,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>8.771929824561403E-3</v>
+        <v>8.5714285714285719E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1899,18 +1885,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>8.771929824561403E-3</v>
+        <v>8.5714285714285719E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2251,14 +2237,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2283,14 +2269,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2315,14 +2301,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2347,14 +2333,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2413,18 +2399,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>874</v>
+        <v>890</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2448,18 +2434,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2483,18 +2469,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2566,14 +2552,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2731,7 +2717,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2799,14 +2785,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2840,14 +2826,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2881,14 +2867,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2923,14 +2909,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2965,14 +2951,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -3006,14 +2992,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3047,14 +3033,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3088,14 +3074,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3129,14 +3115,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3164,14 +3150,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3199,14 +3185,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-64</v>
+        <v>-72</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3234,14 +3220,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-62</v>
+        <v>-70</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3270,14 +3256,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3386,7 +3372,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3865,69 +3851,68 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="85" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="72" t="s">
+    <row r="20" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="73">
+      <c r="E20" s="81">
         <v>46221</v>
       </c>
-      <c r="F20" s="73">
+      <c r="F20" s="81">
         <v>46245</v>
       </c>
-      <c r="G20" s="72">
+      <c r="G20" s="82">
         <f>F20-E20</f>
         <v>24</v>
       </c>
-      <c r="H20" s="72">
+      <c r="H20" s="80">
         <v>12</v>
       </c>
-      <c r="I20" s="86">
+      <c r="I20" s="83">
         <f>J20/H20</f>
         <v>0.91666666666666663</v>
       </c>
-      <c r="J20" s="72">
+      <c r="J20" s="80">
         <v>11</v>
       </c>
-      <c r="K20" s="86"/>
-    </row>
-    <row r="21" spans="1:11" s="85" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="72" t="s">
+    </row>
+    <row r="21" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="73">
+      <c r="E21" s="81">
         <v>46223</v>
       </c>
-      <c r="F21" s="73">
+      <c r="F21" s="81">
         <v>46245</v>
       </c>
-      <c r="G21" s="72">
+      <c r="G21" s="82">
         <f>F21-E21</f>
         <v>22</v>
       </c>
-      <c r="H21" s="72">
+      <c r="H21" s="80">
         <v>12</v>
       </c>
-      <c r="I21" s="86">
+      <c r="I21" s="83">
         <f>J21/H21</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="J21" s="72">
+      <c r="J21" s="80">
         <v>7</v>
       </c>
-      <c r="K21" s="86"/>
+      <c r="K21" s="80"/>
     </row>
     <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17" t="s">
@@ -3943,8 +3928,8 @@
         <v>98</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" ref="F21:F23" ca="1" si="0">TODAY()</f>
-        <v>46246</v>
+        <f t="shared" ref="F22:F23" ca="1" si="0">TODAY()</f>
+        <v>46254</v>
       </c>
       <c r="G22" s="17" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -3973,11 +3958,11 @@
       </c>
       <c r="F23" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="G23" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H23" s="17">
         <v>10</v>
@@ -4151,11 +4136,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4183,11 +4168,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA29442-169B-4057-A99F-E926AA41346E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643A7144-1555-4402-9C32-9B2B3D2207B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="99">
   <si>
     <t>HOJE</t>
   </si>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1515,18 +1515,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.1319910514541388E-2</v>
+        <v>3.0837004405286344E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.9893617021276598E-2</v>
+        <v>3.91644908616188E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-344</v>
+        <v>-351</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-344</v>
+        <v>-351</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1790,18 +1790,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>8.5714285714285719E-3</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1853,18 +1853,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>8.5714285714285719E-3</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1885,18 +1885,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>8.5714285714285719E-3</v>
+        <v>8.4033613445378148E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2301,14 +2301,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2399,18 +2399,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2434,18 +2434,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2469,18 +2469,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2717,7 +2717,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2909,14 +2909,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2951,14 +2951,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3033,14 +3033,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3115,14 +3115,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3185,14 +3185,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-72</v>
+        <v>-79</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-70</v>
+        <v>-77</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3256,14 +3256,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3280,12 +3280,40 @@
       </c>
     </row>
     <row r="16" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="22"/>
+      <c r="C16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46261</v>
+      </c>
+      <c r="G16" s="18">
+        <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
+        <v>46261</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" ref="H16" ca="1" si="5">G16-F16</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="72">
+        <v>6</v>
+      </c>
+      <c r="K16" s="72">
+        <v>6</v>
+      </c>
+      <c r="L16" s="22">
+        <f>K16/J16</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F17" s="18"/>
@@ -3372,7 +3400,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3882,8 +3910,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="76" t="s">
+    <row r="21" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="80" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="80" t="s">
@@ -3912,7 +3940,6 @@
       <c r="J21" s="80">
         <v>7</v>
       </c>
-      <c r="K21" s="80"/>
     </row>
     <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17" t="s">
@@ -3929,7 +3956,7 @@
       </c>
       <c r="F22" s="18">
         <f t="shared" ref="F22:F23" ca="1" si="0">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="G22" s="17" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -3943,36 +3970,37 @@
       <c r="J22" s="17"/>
       <c r="K22" s="22"/>
     </row>
-    <row r="23" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="17" t="s">
+    <row r="23" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="81">
         <v>46237</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="81">
         <f t="shared" ca="1" si="0"/>
-        <v>46254</v>
-      </c>
-      <c r="G23" s="17">
+        <v>46261</v>
+      </c>
+      <c r="G23" s="82">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="H23" s="17">
+        <v>24</v>
+      </c>
+      <c r="H23" s="80">
         <v>10</v>
       </c>
       <c r="I23" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="22"/>
+        <v>0.6</v>
+      </c>
+      <c r="J23" s="80">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B24" s="72"/>
@@ -4136,11 +4164,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4168,11 +4196,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643A7144-1555-4402-9C32-9B2B3D2207B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A143F4CB-6750-4D2A-A2C8-5E2EFD249456}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1515,18 +1515,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0837004405286344E-2</v>
+        <v>3.0769230769230771E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.91644908616188E-2</v>
+        <v>3.90625E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-351</v>
+        <v>-352</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-351</v>
+        <v>-352</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1790,18 +1790,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>8.4033613445378148E-3</v>
+        <v>8.3798882681564244E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1853,18 +1853,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>8.4033613445378148E-3</v>
+        <v>8.3798882681564244E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1885,18 +1885,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>8.4033613445378148E-3</v>
+        <v>8.3798882681564244E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2301,14 +2301,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2399,18 +2399,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2434,18 +2434,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2469,18 +2469,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2717,7 +2717,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2909,14 +2909,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2951,14 +2951,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3033,14 +3033,14 @@
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G9" s="18">
         <v>46082</v>
       </c>
       <c r="H9" s="17">
         <f ca="1">F9-G9</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>54</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3115,14 +3115,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3185,14 +3185,14 @@
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G13" s="73">
         <v>46182</v>
       </c>
       <c r="H13" s="17">
         <f ca="1">G13-F13</f>
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>54</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G14" s="77">
         <v>46184</v>
       </c>
       <c r="H14" s="17">
         <f ca="1">G14-F14</f>
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>54</v>
@@ -3256,14 +3256,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f ca="1">F15-G15</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3291,11 +3291,11 @@
       </c>
       <c r="F16" s="18">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G16" s="18">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H16" s="17">
         <f t="shared" ref="H16" ca="1" si="5">G16-F16</f>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="F22" s="18">
         <f t="shared" ref="F22:F23" ca="1" si="0">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G22" s="17" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -3984,12 +3984,11 @@
         <v>46237</v>
       </c>
       <c r="F23" s="81">
-        <f t="shared" ca="1" si="0"/>
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="G23" s="82">
-        <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="H23" s="80">
         <v>10</v>
@@ -4164,11 +4163,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4196,11 +4195,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>
